--- a/2.proyecto.model.r.piedras/Informe_Fanny.xlsx
+++ b/2.proyecto.model.r.piedras/Informe_Fanny.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Proyectos\2024\1. Modelación matemática R. Piedra\2026\datos\piedras_iib_proyecto\data\raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Javier Rodriguez\Documents\GitHub\Proyectos\2.proyecto.model.r.piedras\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B69124D-DDAD-43E1-83A3-D7DB3E83503A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7EAF3441-F6A6-45AF-AE78-96A529A4CE11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" activeTab="10" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="859" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Coordenadas " sheetId="17" r:id="rId1"/>
@@ -24,6 +24,7 @@
     <sheet name="IIBPeces" sheetId="28" r:id="rId9"/>
     <sheet name="IIBMA" sheetId="16" r:id="rId10"/>
     <sheet name="IIBPef" sheetId="22" r:id="rId11"/>
+    <sheet name="IIBVeg" sheetId="29" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">IIBMA!$A$35:$G$78</definedName>
@@ -4548,38 +4549,41 @@
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="21" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
@@ -4608,23 +4612,20 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4641,14 +4642,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4701,6 +4696,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -4716,17 +4714,20 @@
     <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -5283,12 +5284,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A1" s="117" t="s">
+      <c r="A1" s="126" t="s">
         <v>231</v>
       </c>
-      <c r="B1" s="117"/>
-      <c r="C1" s="117"/>
-      <c r="D1" s="117"/>
+      <c r="B1" s="126"/>
+      <c r="C1" s="126"/>
+      <c r="D1" s="126"/>
     </row>
     <row r="2" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A2" s="30"/>
@@ -5316,15 +5317,15 @@
       </c>
     </row>
     <row r="5" spans="1:20" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="119" t="s">
+      <c r="A5" s="166" t="s">
         <v>236</v>
       </c>
-      <c r="B5" s="119"/>
-      <c r="C5" s="119"/>
-      <c r="D5" s="119"/>
-      <c r="E5" s="119"/>
-      <c r="F5" s="119"/>
-      <c r="G5" s="119"/>
+      <c r="B5" s="166"/>
+      <c r="C5" s="166"/>
+      <c r="D5" s="166"/>
+      <c r="E5" s="166"/>
+      <c r="F5" s="166"/>
+      <c r="G5" s="166"/>
       <c r="L5" s="30" t="s">
         <v>237</v>
       </c>
@@ -5531,7 +5532,7 @@
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A16" s="121" t="s">
+      <c r="A16" s="117" t="s">
         <v>277</v>
       </c>
       <c r="B16" s="19" t="s">
@@ -5540,11 +5541,11 @@
       <c r="C16" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="D16" s="121" t="s">
+      <c r="D16" s="117" t="s">
         <v>279</v>
       </c>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
       <c r="G16" s="33" t="s">
         <v>280</v>
       </c>
@@ -5556,33 +5557,33 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="121"/>
+      <c r="A17" s="117"/>
       <c r="B17" s="19" t="s">
         <v>283</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>250</v>
       </c>
-      <c r="D17" s="121" t="s">
+      <c r="D17" s="117" t="s">
         <v>284</v>
       </c>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
       <c r="G17" s="33" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="121"/>
+      <c r="A18" s="117"/>
       <c r="B18" s="51" t="s">
         <v>285</v>
       </c>
       <c r="C18" s="19"/>
-      <c r="D18" s="121" t="s">
+      <c r="D18" s="117" t="s">
         <v>286</v>
       </c>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
       <c r="G18" s="33"/>
     </row>
     <row r="19" spans="1:7" ht="45" x14ac:dyDescent="0.25">
@@ -5593,11 +5594,11 @@
         <v>288</v>
       </c>
       <c r="C19" s="19"/>
-      <c r="D19" s="121" t="s">
+      <c r="D19" s="117" t="s">
         <v>289</v>
       </c>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
       <c r="G19" s="33" t="s">
         <v>290</v>
       </c>
@@ -5612,17 +5613,17 @@
       <c r="C20" s="19" t="s">
         <v>293</v>
       </c>
-      <c r="D20" s="121" t="s">
+      <c r="D20" s="117" t="s">
         <v>294</v>
       </c>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
       <c r="G20" s="33" t="s">
         <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="122" t="s">
+      <c r="A21" s="120" t="s">
         <v>295</v>
       </c>
       <c r="B21" s="19" t="s">
@@ -5631,79 +5632,79 @@
       <c r="C21" s="19" t="s">
         <v>297</v>
       </c>
-      <c r="D21" s="121" t="s">
+      <c r="D21" s="117" t="s">
         <v>298</v>
       </c>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
       <c r="G21" s="33" t="s">
         <v>299</v>
       </c>
     </row>
     <row r="22" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="122"/>
+      <c r="A22" s="120"/>
       <c r="B22" s="19" t="s">
         <v>300</v>
       </c>
       <c r="C22" s="19" t="s">
         <v>301</v>
       </c>
-      <c r="D22" s="121" t="s">
+      <c r="D22" s="117" t="s">
         <v>302</v>
       </c>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
       <c r="G22" s="33" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="23" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="122"/>
+      <c r="A23" s="120"/>
       <c r="B23" s="19" t="s">
         <v>304</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>305</v>
       </c>
-      <c r="D23" s="121" t="s">
+      <c r="D23" s="117" t="s">
         <v>306</v>
       </c>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
       <c r="G23" s="33" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="24" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="122"/>
+      <c r="A24" s="120"/>
       <c r="B24" s="19" t="s">
         <v>125</v>
       </c>
       <c r="C24" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="D24" s="125" t="s">
+      <c r="D24" s="174" t="s">
         <v>307</v>
       </c>
-      <c r="E24" s="126"/>
-      <c r="F24" s="127"/>
+      <c r="E24" s="175"/>
+      <c r="F24" s="176"/>
       <c r="G24" s="33" t="s">
         <v>303</v>
       </c>
     </row>
     <row r="25" spans="1:7" ht="47.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="122"/>
+      <c r="A25" s="120"/>
       <c r="B25" s="19" t="s">
         <v>308</v>
       </c>
       <c r="C25" s="19" t="s">
         <v>309</v>
       </c>
-      <c r="D25" s="121" t="s">
+      <c r="D25" s="117" t="s">
         <v>310</v>
       </c>
-      <c r="E25" s="121"/>
-      <c r="F25" s="121"/>
+      <c r="E25" s="117"/>
+      <c r="F25" s="117"/>
       <c r="G25" s="33" t="s">
         <v>303</v>
       </c>
@@ -5718,11 +5719,11 @@
       <c r="C26" s="19" t="s">
         <v>313</v>
       </c>
-      <c r="D26" s="121" t="s">
+      <c r="D26" s="117" t="s">
         <v>314</v>
       </c>
-      <c r="E26" s="121"/>
-      <c r="F26" s="121"/>
+      <c r="E26" s="117"/>
+      <c r="F26" s="117"/>
       <c r="G26" s="33" t="s">
         <v>315</v>
       </c>
@@ -5735,11 +5736,11 @@
         <v>317</v>
       </c>
       <c r="C27" s="19"/>
-      <c r="D27" s="121" t="s">
+      <c r="D27" s="117" t="s">
         <v>318</v>
       </c>
-      <c r="E27" s="121"/>
-      <c r="F27" s="121"/>
+      <c r="E27" s="117"/>
+      <c r="F27" s="117"/>
       <c r="G27" s="33" t="s">
         <v>280</v>
       </c>
@@ -5781,18 +5782,18 @@
       <c r="G35" s="118" t="s">
         <v>324</v>
       </c>
-      <c r="I35" s="123" t="s">
+      <c r="I35" s="148" t="s">
         <v>103</v>
       </c>
-      <c r="J35" s="120" t="s">
+      <c r="J35" s="172" t="s">
         <v>100</v>
       </c>
-      <c r="K35" s="120" t="s">
+      <c r="K35" s="172" t="s">
         <v>29</v>
       </c>
-      <c r="L35" s="120"/>
-      <c r="M35" s="120"/>
-      <c r="N35" s="124" t="s">
+      <c r="L35" s="172"/>
+      <c r="M35" s="172"/>
+      <c r="N35" s="173" t="s">
         <v>325</v>
       </c>
       <c r="Q35" s="118" t="s">
@@ -5839,8 +5840,8 @@
       </c>
       <c r="F36" s="118"/>
       <c r="G36" s="118"/>
-      <c r="I36" s="123"/>
-      <c r="J36" s="120"/>
+      <c r="I36" s="148"/>
+      <c r="J36" s="172"/>
       <c r="K36" s="44" t="s">
         <v>32</v>
       </c>
@@ -5850,7 +5851,7 @@
       <c r="M36" s="44" t="s">
         <v>34</v>
       </c>
-      <c r="N36" s="124"/>
+      <c r="N36" s="173"/>
       <c r="Q36" s="118"/>
       <c r="R36" s="118"/>
       <c r="S36" s="42" t="s">
@@ -8175,10 +8176,10 @@
       <c r="V77" s="1"/>
     </row>
     <row r="78" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A78" s="120" t="s">
+      <c r="A78" s="172" t="s">
         <v>349</v>
       </c>
-      <c r="B78" s="120"/>
+      <c r="B78" s="172"/>
       <c r="C78" s="1">
         <f>+SUM(C37:C77)</f>
         <v>978</v>
@@ -8218,10 +8219,10 @@
         <f t="shared" si="2"/>
         <v>11</v>
       </c>
-      <c r="Q78" s="120" t="s">
+      <c r="Q78" s="172" t="s">
         <v>349</v>
       </c>
-      <c r="R78" s="120"/>
+      <c r="R78" s="172"/>
       <c r="S78" s="1">
         <f>+SUM(S37:S77)</f>
         <v>978</v>
@@ -8883,10 +8884,10 @@
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="I99" s="120" t="s">
+      <c r="I99" s="172" t="s">
         <v>349</v>
       </c>
-      <c r="J99" s="120"/>
+      <c r="J99" s="172"/>
       <c r="K99" s="1">
         <f>SUM(K37:K98)</f>
         <v>978</v>
@@ -9102,11 +9103,20 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="Q78:R78"/>
-    <mergeCell ref="Q35:Q36"/>
-    <mergeCell ref="R35:R36"/>
-    <mergeCell ref="S35:U35"/>
-    <mergeCell ref="V35:V36"/>
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C35:E35"/>
+    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="F35:F36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="C82:E82"/>
+    <mergeCell ref="I35:I36"/>
+    <mergeCell ref="J35:J36"/>
+    <mergeCell ref="K35:M35"/>
+    <mergeCell ref="I99:J99"/>
     <mergeCell ref="N35:N36"/>
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="D16:F16"/>
@@ -9122,20 +9132,11 @@
     <mergeCell ref="D21:F21"/>
     <mergeCell ref="D24:F24"/>
     <mergeCell ref="G35:G36"/>
-    <mergeCell ref="C82:E82"/>
-    <mergeCell ref="I35:I36"/>
-    <mergeCell ref="J35:J36"/>
-    <mergeCell ref="K35:M35"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="C35:E35"/>
-    <mergeCell ref="A5:G5"/>
-    <mergeCell ref="A78:B78"/>
-    <mergeCell ref="F35:F36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="A16:A18"/>
-    <mergeCell ref="A21:A25"/>
+    <mergeCell ref="Q78:R78"/>
+    <mergeCell ref="Q35:Q36"/>
+    <mergeCell ref="R35:R36"/>
+    <mergeCell ref="S35:U35"/>
+    <mergeCell ref="V35:V36"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -9155,7 +9156,7 @@
     <col min="1" max="1" width="25.5703125" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="4" max="4" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="16.28515625" customWidth="1"/>
+    <col min="7" max="7" width="69.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:7" x14ac:dyDescent="0.25">
@@ -9191,7 +9192,7 @@
       </c>
     </row>
     <row r="7" spans="1:7" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="121" t="s">
+      <c r="A7" s="117" t="s">
         <v>367</v>
       </c>
       <c r="B7" s="47" t="s">
@@ -9200,22 +9201,22 @@
       <c r="C7" s="19" t="s">
         <v>242</v>
       </c>
-      <c r="D7" s="121" t="s">
+      <c r="D7" s="117" t="s">
         <v>369</v>
       </c>
-      <c r="E7" s="121"/>
-      <c r="F7" s="121"/>
+      <c r="E7" s="117"/>
+      <c r="F7" s="117"/>
       <c r="G7" s="41"/>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="121"/>
+      <c r="A8" s="117"/>
       <c r="B8" s="19" t="s">
         <v>370</v>
       </c>
       <c r="C8" s="19"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="121"/>
-      <c r="F8" s="121"/>
+      <c r="D8" s="117"/>
+      <c r="E8" s="117"/>
+      <c r="F8" s="117"/>
       <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
@@ -9226,17 +9227,17 @@
       <c r="C9" s="19" t="s">
         <v>372</v>
       </c>
-      <c r="D9" s="121" t="s">
+      <c r="D9" s="117" t="s">
         <v>373</v>
       </c>
-      <c r="E9" s="121"/>
-      <c r="F9" s="121"/>
+      <c r="E9" s="117"/>
+      <c r="F9" s="117"/>
       <c r="G9" s="41" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="122" t="s">
+      <c r="A10" s="120" t="s">
         <v>375</v>
       </c>
       <c r="B10" s="19" t="s">
@@ -9245,98 +9246,98 @@
       <c r="C10" s="19" t="s">
         <v>377</v>
       </c>
-      <c r="D10" s="121" t="s">
+      <c r="D10" s="117" t="s">
         <v>378</v>
       </c>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
+      <c r="E10" s="117"/>
+      <c r="F10" s="117"/>
       <c r="G10" s="41" t="s">
         <v>379</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="122"/>
+      <c r="A11" s="120"/>
       <c r="B11" s="19" t="s">
         <v>380</v>
       </c>
       <c r="C11" s="19" t="s">
         <v>381</v>
       </c>
-      <c r="D11" s="121" t="s">
+      <c r="D11" s="117" t="s">
         <v>382</v>
       </c>
-      <c r="E11" s="121"/>
-      <c r="F11" s="121"/>
+      <c r="E11" s="117"/>
+      <c r="F11" s="117"/>
       <c r="G11" s="41" t="s">
         <v>383</v>
       </c>
     </row>
     <row r="12" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="122"/>
+      <c r="A12" s="120"/>
       <c r="B12" s="19" t="s">
         <v>384</v>
       </c>
       <c r="C12" s="19" t="s">
         <v>385</v>
       </c>
-      <c r="D12" s="121" t="s">
+      <c r="D12" s="117" t="s">
         <v>382</v>
       </c>
-      <c r="E12" s="121"/>
-      <c r="F12" s="121"/>
+      <c r="E12" s="117"/>
+      <c r="F12" s="117"/>
       <c r="G12" s="41" t="s">
         <v>386</v>
       </c>
     </row>
     <row r="13" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="122"/>
+      <c r="A13" s="120"/>
       <c r="B13" s="19" t="s">
         <v>387</v>
       </c>
       <c r="C13" s="19" t="s">
         <v>388</v>
       </c>
-      <c r="D13" s="121" t="s">
+      <c r="D13" s="117" t="s">
         <v>382</v>
       </c>
-      <c r="E13" s="121"/>
-      <c r="F13" s="121"/>
+      <c r="E13" s="117"/>
+      <c r="F13" s="117"/>
       <c r="G13" s="41" t="s">
         <v>389</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="122"/>
+      <c r="A14" s="120"/>
       <c r="B14" s="19" t="s">
         <v>390</v>
       </c>
       <c r="C14" s="19" t="s">
         <v>391</v>
       </c>
-      <c r="D14" s="121" t="s">
+      <c r="D14" s="117" t="s">
         <v>392</v>
       </c>
-      <c r="E14" s="121"/>
-      <c r="F14" s="121"/>
+      <c r="E14" s="117"/>
+      <c r="F14" s="117"/>
       <c r="G14" s="41"/>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="122"/>
+      <c r="A15" s="120"/>
       <c r="B15" s="1" t="s">
         <v>393</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>394</v>
       </c>
-      <c r="D15" s="121" t="s">
+      <c r="D15" s="117" t="s">
         <v>395</v>
       </c>
-      <c r="E15" s="121"/>
-      <c r="F15" s="121"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
       <c r="G15" s="41"/>
     </row>
     <row r="16" spans="1:7" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="175" t="s">
+      <c r="A16" s="122" t="s">
         <v>396</v>
       </c>
       <c r="B16" s="85" t="s">
@@ -9345,92 +9346,92 @@
       <c r="C16" s="19" t="s">
         <v>398</v>
       </c>
-      <c r="D16" s="121" t="s">
+      <c r="D16" s="117" t="s">
         <v>382</v>
       </c>
-      <c r="E16" s="121"/>
-      <c r="F16" s="121"/>
+      <c r="E16" s="117"/>
+      <c r="F16" s="117"/>
       <c r="G16" s="41" t="s">
         <v>399</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A17" s="175"/>
+      <c r="A17" s="122"/>
       <c r="B17" s="19" t="s">
         <v>400</v>
       </c>
       <c r="C17" s="19" t="s">
         <v>401</v>
       </c>
-      <c r="D17" s="121" t="s">
+      <c r="D17" s="117" t="s">
         <v>392</v>
       </c>
-      <c r="E17" s="121"/>
-      <c r="F17" s="121"/>
+      <c r="E17" s="117"/>
+      <c r="F17" s="117"/>
       <c r="G17" s="41"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A18" s="175"/>
+      <c r="A18" s="122"/>
       <c r="B18" s="19" t="s">
         <v>402</v>
       </c>
       <c r="C18" s="19" t="s">
         <v>403</v>
       </c>
-      <c r="D18" s="121" t="s">
+      <c r="D18" s="117" t="s">
         <v>395</v>
       </c>
-      <c r="E18" s="121"/>
-      <c r="F18" s="121"/>
+      <c r="E18" s="117"/>
+      <c r="F18" s="117"/>
       <c r="G18" s="41"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A19" s="175"/>
+      <c r="A19" s="122"/>
       <c r="B19" s="19" t="s">
         <v>404</v>
       </c>
       <c r="C19" s="19" t="s">
         <v>405</v>
       </c>
-      <c r="D19" s="121" t="s">
+      <c r="D19" s="117" t="s">
         <v>406</v>
       </c>
-      <c r="E19" s="121"/>
-      <c r="F19" s="121"/>
+      <c r="E19" s="117"/>
+      <c r="F19" s="117"/>
       <c r="G19" s="41"/>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A20" s="175"/>
+      <c r="A20" s="122"/>
       <c r="B20" s="19" t="s">
         <v>407</v>
       </c>
       <c r="C20" s="19" t="s">
         <v>408</v>
       </c>
-      <c r="D20" s="121" t="s">
+      <c r="D20" s="117" t="s">
         <v>409</v>
       </c>
-      <c r="E20" s="121"/>
-      <c r="F20" s="121"/>
+      <c r="E20" s="117"/>
+      <c r="F20" s="117"/>
       <c r="G20" s="41"/>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A21" s="175"/>
+      <c r="A21" s="122"/>
       <c r="B21" s="19" t="s">
         <v>410</v>
       </c>
       <c r="C21" s="19" t="s">
         <v>411</v>
       </c>
-      <c r="D21" s="121" t="s">
+      <c r="D21" s="117" t="s">
         <v>412</v>
       </c>
-      <c r="E21" s="121"/>
-      <c r="F21" s="121"/>
+      <c r="E21" s="117"/>
+      <c r="F21" s="117"/>
       <c r="G21" s="41"/>
     </row>
     <row r="22" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="176" t="s">
+      <c r="A22" s="123" t="s">
         <v>413</v>
       </c>
       <c r="B22" s="47" t="s">
@@ -9439,26 +9440,26 @@
       <c r="C22" s="19" t="s">
         <v>415</v>
       </c>
-      <c r="D22" s="121" t="s">
+      <c r="D22" s="117" t="s">
         <v>382</v>
       </c>
-      <c r="E22" s="121"/>
-      <c r="F22" s="121"/>
+      <c r="E22" s="117"/>
+      <c r="F22" s="117"/>
       <c r="G22" s="41"/>
     </row>
     <row r="23" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="176"/>
+      <c r="A23" s="123"/>
       <c r="B23" s="47" t="s">
         <v>416</v>
       </c>
       <c r="C23" s="19" t="s">
         <v>417</v>
       </c>
-      <c r="D23" s="121" t="s">
+      <c r="D23" s="117" t="s">
         <v>382</v>
       </c>
-      <c r="E23" s="121"/>
-      <c r="F23" s="121"/>
+      <c r="E23" s="117"/>
+      <c r="F23" s="117"/>
       <c r="G23" s="41"/>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.25">
@@ -9489,105 +9490,105 @@
       <c r="G26" s="72"/>
     </row>
     <row r="29" spans="1:9" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="174" t="s">
+      <c r="A29" s="121" t="s">
         <v>418</v>
       </c>
-      <c r="B29" s="174"/>
-      <c r="C29" s="174"/>
-      <c r="D29" s="174"/>
-      <c r="E29" s="174"/>
-      <c r="F29" s="174"/>
-      <c r="G29" s="174"/>
-      <c r="H29" s="174"/>
-      <c r="I29" s="174"/>
+      <c r="B29" s="121"/>
+      <c r="C29" s="121"/>
+      <c r="D29" s="121"/>
+      <c r="E29" s="121"/>
+      <c r="F29" s="121"/>
+      <c r="G29" s="121"/>
+      <c r="H29" s="121"/>
+      <c r="I29" s="121"/>
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A30" s="174"/>
-      <c r="B30" s="174"/>
-      <c r="C30" s="174"/>
-      <c r="D30" s="174"/>
-      <c r="E30" s="174"/>
-      <c r="F30" s="174"/>
-      <c r="G30" s="174"/>
-      <c r="H30" s="174"/>
-      <c r="I30" s="174"/>
+      <c r="A30" s="121"/>
+      <c r="B30" s="121"/>
+      <c r="C30" s="121"/>
+      <c r="D30" s="121"/>
+      <c r="E30" s="121"/>
+      <c r="F30" s="121"/>
+      <c r="G30" s="121"/>
+      <c r="H30" s="121"/>
+      <c r="I30" s="121"/>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A31" s="174"/>
-      <c r="B31" s="174"/>
-      <c r="C31" s="174"/>
-      <c r="D31" s="174"/>
-      <c r="E31" s="174"/>
-      <c r="F31" s="174"/>
-      <c r="G31" s="174"/>
-      <c r="H31" s="174"/>
-      <c r="I31" s="174"/>
+      <c r="A31" s="121"/>
+      <c r="B31" s="121"/>
+      <c r="C31" s="121"/>
+      <c r="D31" s="121"/>
+      <c r="E31" s="121"/>
+      <c r="F31" s="121"/>
+      <c r="G31" s="121"/>
+      <c r="H31" s="121"/>
+      <c r="I31" s="121"/>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A32" s="174"/>
-      <c r="B32" s="174"/>
-      <c r="C32" s="174"/>
-      <c r="D32" s="174"/>
-      <c r="E32" s="174"/>
-      <c r="F32" s="174"/>
-      <c r="G32" s="174"/>
-      <c r="H32" s="174"/>
-      <c r="I32" s="174"/>
+      <c r="A32" s="121"/>
+      <c r="B32" s="121"/>
+      <c r="C32" s="121"/>
+      <c r="D32" s="121"/>
+      <c r="E32" s="121"/>
+      <c r="F32" s="121"/>
+      <c r="G32" s="121"/>
+      <c r="H32" s="121"/>
+      <c r="I32" s="121"/>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A33" s="174"/>
-      <c r="B33" s="174"/>
-      <c r="C33" s="174"/>
-      <c r="D33" s="174"/>
-      <c r="E33" s="174"/>
-      <c r="F33" s="174"/>
-      <c r="G33" s="174"/>
-      <c r="H33" s="174"/>
-      <c r="I33" s="174"/>
+      <c r="A33" s="121"/>
+      <c r="B33" s="121"/>
+      <c r="C33" s="121"/>
+      <c r="D33" s="121"/>
+      <c r="E33" s="121"/>
+      <c r="F33" s="121"/>
+      <c r="G33" s="121"/>
+      <c r="H33" s="121"/>
+      <c r="I33" s="121"/>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A34" s="174"/>
-      <c r="B34" s="174"/>
-      <c r="C34" s="174"/>
-      <c r="D34" s="174"/>
-      <c r="E34" s="174"/>
-      <c r="F34" s="174"/>
-      <c r="G34" s="174"/>
-      <c r="H34" s="174"/>
-      <c r="I34" s="174"/>
+      <c r="A34" s="121"/>
+      <c r="B34" s="121"/>
+      <c r="C34" s="121"/>
+      <c r="D34" s="121"/>
+      <c r="E34" s="121"/>
+      <c r="F34" s="121"/>
+      <c r="G34" s="121"/>
+      <c r="H34" s="121"/>
+      <c r="I34" s="121"/>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A35" s="174"/>
-      <c r="B35" s="174"/>
-      <c r="C35" s="174"/>
-      <c r="D35" s="174"/>
-      <c r="E35" s="174"/>
-      <c r="F35" s="174"/>
-      <c r="G35" s="174"/>
-      <c r="H35" s="174"/>
-      <c r="I35" s="174"/>
+      <c r="A35" s="121"/>
+      <c r="B35" s="121"/>
+      <c r="C35" s="121"/>
+      <c r="D35" s="121"/>
+      <c r="E35" s="121"/>
+      <c r="F35" s="121"/>
+      <c r="G35" s="121"/>
+      <c r="H35" s="121"/>
+      <c r="I35" s="121"/>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A36" s="174"/>
-      <c r="B36" s="174"/>
-      <c r="C36" s="174"/>
-      <c r="D36" s="174"/>
-      <c r="E36" s="174"/>
-      <c r="F36" s="174"/>
-      <c r="G36" s="174"/>
-      <c r="H36" s="174"/>
-      <c r="I36" s="174"/>
+      <c r="A36" s="121"/>
+      <c r="B36" s="121"/>
+      <c r="C36" s="121"/>
+      <c r="D36" s="121"/>
+      <c r="E36" s="121"/>
+      <c r="F36" s="121"/>
+      <c r="G36" s="121"/>
+      <c r="H36" s="121"/>
+      <c r="I36" s="121"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A37" s="174"/>
-      <c r="B37" s="174"/>
-      <c r="C37" s="174"/>
-      <c r="D37" s="174"/>
-      <c r="E37" s="174"/>
-      <c r="F37" s="174"/>
-      <c r="G37" s="174"/>
-      <c r="H37" s="174"/>
-      <c r="I37" s="174"/>
+      <c r="A37" s="121"/>
+      <c r="B37" s="121"/>
+      <c r="C37" s="121"/>
+      <c r="D37" s="121"/>
+      <c r="E37" s="121"/>
+      <c r="F37" s="121"/>
+      <c r="G37" s="121"/>
+      <c r="H37" s="121"/>
+      <c r="I37" s="121"/>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" s="34" t="s">
@@ -9603,11 +9604,11 @@
       <c r="A52" s="73"/>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="B53" s="173" t="s">
+      <c r="B53" s="119" t="s">
         <v>420</v>
       </c>
-      <c r="C53" s="173"/>
-      <c r="D53" s="173"/>
+      <c r="C53" s="119"/>
+      <c r="D53" s="119"/>
       <c r="G53" s="80" t="s">
         <v>421</v>
       </c>
@@ -10107,14 +10108,6 @@
     </row>
   </sheetData>
   <mergeCells count="24">
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D6:F6"/>
-    <mergeCell ref="A7:A8"/>
-    <mergeCell ref="D7:F7"/>
-    <mergeCell ref="D8:F8"/>
-    <mergeCell ref="D9:F9"/>
     <mergeCell ref="B53:D53"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="D10:F10"/>
@@ -10131,8 +10124,28 @@
     <mergeCell ref="D23:F23"/>
     <mergeCell ref="A22:A23"/>
     <mergeCell ref="D18:F18"/>
+    <mergeCell ref="D20:F20"/>
+    <mergeCell ref="D21:F21"/>
+    <mergeCell ref="D19:F19"/>
+    <mergeCell ref="D6:F6"/>
+    <mergeCell ref="A7:A8"/>
+    <mergeCell ref="D7:F7"/>
+    <mergeCell ref="D8:F8"/>
+    <mergeCell ref="D9:F9"/>
   </mergeCells>
   <phoneticPr fontId="12" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8BACCBCD-2F07-4CD0-A16E-11C9BA29A780}">
+  <sheetPr>
+    <tabColor rgb="FF0070C0"/>
+  </sheetPr>
+  <dimension ref="A1"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -10160,53 +10173,53 @@
       <c r="A5" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="B5" s="140" t="s">
+      <c r="B5" s="124" t="s">
         <v>675</v>
       </c>
-      <c r="C5" s="140"/>
-      <c r="D5" s="140"/>
-      <c r="E5" s="140"/>
-      <c r="F5" s="140"/>
-      <c r="G5" s="140"/>
+      <c r="C5" s="124"/>
+      <c r="D5" s="124"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="124"/>
+      <c r="G5" s="124"/>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="B6" s="140" t="s">
+      <c r="B6" s="124" t="s">
         <v>677</v>
       </c>
-      <c r="C6" s="140"/>
-      <c r="D6" s="140"/>
-      <c r="E6" s="140"/>
-      <c r="F6" s="140"/>
-      <c r="G6" s="140"/>
+      <c r="C6" s="124"/>
+      <c r="D6" s="124"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="124"/>
+      <c r="G6" s="124"/>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="B7" s="140" t="s">
+      <c r="B7" s="124" t="s">
         <v>678</v>
       </c>
-      <c r="C7" s="140"/>
-      <c r="D7" s="140"/>
-      <c r="E7" s="140"/>
-      <c r="F7" s="140"/>
-      <c r="G7" s="140"/>
+      <c r="C7" s="124"/>
+      <c r="D7" s="124"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="124"/>
+      <c r="G7" s="124"/>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>527</v>
       </c>
-      <c r="B8" s="140" t="s">
+      <c r="B8" s="124" t="s">
         <v>679</v>
       </c>
-      <c r="C8" s="140"/>
-      <c r="D8" s="140"/>
-      <c r="E8" s="140"/>
-      <c r="F8" s="140"/>
-      <c r="G8" s="140"/>
+      <c r="C8" s="124"/>
+      <c r="D8" s="124"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="124"/>
+      <c r="G8" s="124"/>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
@@ -10217,10 +10230,10 @@
       <c r="A12" s="4"/>
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="117" t="s">
+      <c r="A13" s="126" t="s">
         <v>681</v>
       </c>
-      <c r="B13" s="117"/>
+      <c r="B13" s="126"/>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
@@ -10235,17 +10248,17 @@
       <c r="C15" s="61" t="s">
         <v>683</v>
       </c>
-      <c r="D15" s="137" t="s">
+      <c r="D15" s="125" t="s">
         <v>684</v>
       </c>
-      <c r="E15" s="137"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="137"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="137"/>
-      <c r="J15" s="137"/>
-      <c r="K15" s="137"/>
-      <c r="L15" s="137"/>
+      <c r="E15" s="125"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="125"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="125"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="125"/>
+      <c r="L15" s="125"/>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -10255,17 +10268,17 @@
         <v>686</v>
       </c>
       <c r="C16" s="105"/>
-      <c r="D16" s="140" t="s">
+      <c r="D16" s="124" t="s">
         <v>687</v>
       </c>
-      <c r="E16" s="140"/>
-      <c r="F16" s="140"/>
-      <c r="G16" s="140"/>
-      <c r="H16" s="140"/>
-      <c r="I16" s="140"/>
-      <c r="J16" s="140"/>
-      <c r="K16" s="140"/>
-      <c r="L16" s="140"/>
+      <c r="E16" s="124"/>
+      <c r="F16" s="124"/>
+      <c r="G16" s="124"/>
+      <c r="H16" s="124"/>
+      <c r="I16" s="124"/>
+      <c r="J16" s="124"/>
+      <c r="K16" s="124"/>
+      <c r="L16" s="124"/>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
@@ -10275,17 +10288,17 @@
         <v>282</v>
       </c>
       <c r="C17" s="99"/>
-      <c r="D17" s="140" t="s">
+      <c r="D17" s="124" t="s">
         <v>689</v>
       </c>
-      <c r="E17" s="140"/>
-      <c r="F17" s="140"/>
-      <c r="G17" s="140"/>
-      <c r="H17" s="140"/>
-      <c r="I17" s="140"/>
-      <c r="J17" s="140"/>
-      <c r="K17" s="140"/>
-      <c r="L17" s="140"/>
+      <c r="E17" s="124"/>
+      <c r="F17" s="124"/>
+      <c r="G17" s="124"/>
+      <c r="H17" s="124"/>
+      <c r="I17" s="124"/>
+      <c r="J17" s="124"/>
+      <c r="K17" s="124"/>
+      <c r="L17" s="124"/>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -10295,17 +10308,17 @@
         <v>691</v>
       </c>
       <c r="C18" s="98"/>
-      <c r="D18" s="140" t="s">
+      <c r="D18" s="124" t="s">
         <v>692</v>
       </c>
-      <c r="E18" s="140"/>
-      <c r="F18" s="140"/>
-      <c r="G18" s="140"/>
-      <c r="H18" s="140"/>
-      <c r="I18" s="140"/>
-      <c r="J18" s="140"/>
-      <c r="K18" s="140"/>
-      <c r="L18" s="140"/>
+      <c r="E18" s="124"/>
+      <c r="F18" s="124"/>
+      <c r="G18" s="124"/>
+      <c r="H18" s="124"/>
+      <c r="I18" s="124"/>
+      <c r="J18" s="124"/>
+      <c r="K18" s="124"/>
+      <c r="L18" s="124"/>
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
@@ -10315,17 +10328,17 @@
         <v>542</v>
       </c>
       <c r="C19" s="100"/>
-      <c r="D19" s="140" t="s">
+      <c r="D19" s="124" t="s">
         <v>694</v>
       </c>
-      <c r="E19" s="140"/>
-      <c r="F19" s="140"/>
-      <c r="G19" s="140"/>
-      <c r="H19" s="140"/>
-      <c r="I19" s="140"/>
-      <c r="J19" s="140"/>
-      <c r="K19" s="140"/>
-      <c r="L19" s="140"/>
+      <c r="E19" s="124"/>
+      <c r="F19" s="124"/>
+      <c r="G19" s="124"/>
+      <c r="H19" s="124"/>
+      <c r="I19" s="124"/>
+      <c r="J19" s="124"/>
+      <c r="K19" s="124"/>
+      <c r="L19" s="124"/>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
@@ -10335,17 +10348,17 @@
         <v>266</v>
       </c>
       <c r="C20" s="106"/>
-      <c r="D20" s="140" t="s">
+      <c r="D20" s="124" t="s">
         <v>696</v>
       </c>
-      <c r="E20" s="140"/>
-      <c r="F20" s="140"/>
-      <c r="G20" s="140"/>
-      <c r="H20" s="140"/>
-      <c r="I20" s="140"/>
-      <c r="J20" s="140"/>
-      <c r="K20" s="140"/>
-      <c r="L20" s="140"/>
+      <c r="E20" s="124"/>
+      <c r="F20" s="124"/>
+      <c r="G20" s="124"/>
+      <c r="H20" s="124"/>
+      <c r="I20" s="124"/>
+      <c r="J20" s="124"/>
+      <c r="K20" s="124"/>
+      <c r="L20" s="124"/>
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="104" t="s">
@@ -10415,53 +10428,53 @@
       <c r="A36" s="104"/>
     </row>
     <row r="37" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="128" t="s">
+      <c r="A37" s="129" t="s">
         <v>790</v>
       </c>
-      <c r="B37" s="129"/>
-      <c r="C37" s="130"/>
+      <c r="B37" s="130"/>
+      <c r="C37" s="131"/>
       <c r="D37" s="108"/>
       <c r="E37" s="108"/>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A38" s="131"/>
-      <c r="B38" s="132"/>
-      <c r="C38" s="133"/>
+      <c r="A38" s="132"/>
+      <c r="B38" s="133"/>
+      <c r="C38" s="134"/>
       <c r="D38" s="108"/>
       <c r="E38" s="108"/>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A39" s="131"/>
-      <c r="B39" s="132"/>
-      <c r="C39" s="133"/>
+      <c r="A39" s="132"/>
+      <c r="B39" s="133"/>
+      <c r="C39" s="134"/>
       <c r="D39" s="108"/>
       <c r="E39" s="108"/>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A40" s="131"/>
-      <c r="B40" s="132"/>
-      <c r="C40" s="133"/>
+      <c r="A40" s="132"/>
+      <c r="B40" s="133"/>
+      <c r="C40" s="134"/>
       <c r="D40" s="108"/>
       <c r="E40" s="108"/>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A41" s="131"/>
-      <c r="B41" s="132"/>
-      <c r="C41" s="133"/>
+      <c r="A41" s="132"/>
+      <c r="B41" s="133"/>
+      <c r="C41" s="134"/>
       <c r="D41" s="108"/>
       <c r="E41" s="108"/>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A42" s="131"/>
-      <c r="B42" s="132"/>
-      <c r="C42" s="133"/>
+      <c r="A42" s="132"/>
+      <c r="B42" s="133"/>
+      <c r="C42" s="134"/>
       <c r="D42" s="108"/>
       <c r="E42" s="108"/>
     </row>
     <row r="43" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="134"/>
-      <c r="B43" s="135"/>
-      <c r="C43" s="136"/>
+      <c r="A43" s="135"/>
+      <c r="B43" s="136"/>
+      <c r="C43" s="137"/>
       <c r="D43" s="108"/>
       <c r="E43" s="108"/>
     </row>
@@ -10475,17 +10488,17 @@
       <c r="C45" s="107" t="s">
         <v>707</v>
       </c>
-      <c r="D45" s="138" t="s">
+      <c r="D45" s="127" t="s">
         <v>706</v>
       </c>
-      <c r="E45" s="139"/>
-      <c r="F45" s="139"/>
-      <c r="G45" s="139"/>
-      <c r="H45" s="139"/>
-      <c r="I45" s="139"/>
-      <c r="J45" s="139"/>
-      <c r="K45" s="139"/>
-      <c r="L45" s="139"/>
+      <c r="E45" s="128"/>
+      <c r="F45" s="128"/>
+      <c r="G45" s="128"/>
+      <c r="H45" s="128"/>
+      <c r="I45" s="128"/>
+      <c r="J45" s="128"/>
+      <c r="K45" s="128"/>
+      <c r="L45" s="128"/>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" s="41" t="s">
@@ -10497,17 +10510,17 @@
       <c r="C46" s="33" t="s">
         <v>786</v>
       </c>
-      <c r="D46" s="121" t="s">
+      <c r="D46" s="117" t="s">
         <v>789</v>
       </c>
-      <c r="E46" s="121"/>
-      <c r="F46" s="121"/>
-      <c r="G46" s="121"/>
-      <c r="H46" s="121"/>
-      <c r="I46" s="121"/>
-      <c r="J46" s="121"/>
-      <c r="K46" s="121"/>
-      <c r="L46" s="121"/>
+      <c r="E46" s="117"/>
+      <c r="F46" s="117"/>
+      <c r="G46" s="117"/>
+      <c r="H46" s="117"/>
+      <c r="I46" s="117"/>
+      <c r="J46" s="117"/>
+      <c r="K46" s="117"/>
+      <c r="L46" s="117"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" s="41" t="s">
@@ -10519,17 +10532,17 @@
       <c r="C47" s="33" t="s">
         <v>781</v>
       </c>
-      <c r="D47" s="121" t="s">
+      <c r="D47" s="117" t="s">
         <v>734</v>
       </c>
-      <c r="E47" s="121"/>
-      <c r="F47" s="121"/>
-      <c r="G47" s="121"/>
-      <c r="H47" s="121"/>
-      <c r="I47" s="121"/>
-      <c r="J47" s="121"/>
-      <c r="K47" s="121"/>
-      <c r="L47" s="121"/>
+      <c r="E47" s="117"/>
+      <c r="F47" s="117"/>
+      <c r="G47" s="117"/>
+      <c r="H47" s="117"/>
+      <c r="I47" s="117"/>
+      <c r="J47" s="117"/>
+      <c r="K47" s="117"/>
+      <c r="L47" s="117"/>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" s="41" t="s">
@@ -10541,17 +10554,17 @@
       <c r="C48" s="33" t="s">
         <v>782</v>
       </c>
-      <c r="D48" s="121" t="s">
+      <c r="D48" s="117" t="s">
         <v>736</v>
       </c>
-      <c r="E48" s="121"/>
-      <c r="F48" s="121"/>
-      <c r="G48" s="121"/>
-      <c r="H48" s="121"/>
-      <c r="I48" s="121"/>
-      <c r="J48" s="121"/>
-      <c r="K48" s="121"/>
-      <c r="L48" s="121"/>
+      <c r="E48" s="117"/>
+      <c r="F48" s="117"/>
+      <c r="G48" s="117"/>
+      <c r="H48" s="117"/>
+      <c r="I48" s="117"/>
+      <c r="J48" s="117"/>
+      <c r="K48" s="117"/>
+      <c r="L48" s="117"/>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="41" t="s">
@@ -10563,17 +10576,17 @@
       <c r="C49" s="33" t="s">
         <v>783</v>
       </c>
-      <c r="D49" s="121" t="s">
+      <c r="D49" s="117" t="s">
         <v>738</v>
       </c>
-      <c r="E49" s="121"/>
-      <c r="F49" s="121"/>
-      <c r="G49" s="121"/>
-      <c r="H49" s="121"/>
-      <c r="I49" s="121"/>
-      <c r="J49" s="121"/>
-      <c r="K49" s="121"/>
-      <c r="L49" s="121"/>
+      <c r="E49" s="117"/>
+      <c r="F49" s="117"/>
+      <c r="G49" s="117"/>
+      <c r="H49" s="117"/>
+      <c r="I49" s="117"/>
+      <c r="J49" s="117"/>
+      <c r="K49" s="117"/>
+      <c r="L49" s="117"/>
     </row>
     <row r="50" spans="1:12" ht="30" x14ac:dyDescent="0.25">
       <c r="A50" s="41" t="s">
@@ -10585,17 +10598,17 @@
       <c r="C50" s="33" t="s">
         <v>785</v>
       </c>
-      <c r="D50" s="121" t="s">
+      <c r="D50" s="117" t="s">
         <v>742</v>
       </c>
-      <c r="E50" s="121"/>
-      <c r="F50" s="121"/>
-      <c r="G50" s="121"/>
-      <c r="H50" s="121"/>
-      <c r="I50" s="121"/>
-      <c r="J50" s="121"/>
-      <c r="K50" s="121"/>
-      <c r="L50" s="121"/>
+      <c r="E50" s="117"/>
+      <c r="F50" s="117"/>
+      <c r="G50" s="117"/>
+      <c r="H50" s="117"/>
+      <c r="I50" s="117"/>
+      <c r="J50" s="117"/>
+      <c r="K50" s="117"/>
+      <c r="L50" s="117"/>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="41" t="s">
@@ -10607,17 +10620,17 @@
       <c r="C51" s="33" t="s">
         <v>784</v>
       </c>
-      <c r="D51" s="121" t="s">
+      <c r="D51" s="117" t="s">
         <v>740</v>
       </c>
-      <c r="E51" s="121"/>
-      <c r="F51" s="121"/>
-      <c r="G51" s="121"/>
-      <c r="H51" s="121"/>
-      <c r="I51" s="121"/>
-      <c r="J51" s="121"/>
-      <c r="K51" s="121"/>
-      <c r="L51" s="121"/>
+      <c r="E51" s="117"/>
+      <c r="F51" s="117"/>
+      <c r="G51" s="117"/>
+      <c r="H51" s="117"/>
+      <c r="I51" s="117"/>
+      <c r="J51" s="117"/>
+      <c r="K51" s="117"/>
+      <c r="L51" s="117"/>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="41" t="s">
@@ -10629,17 +10642,17 @@
       <c r="C52" s="41" t="s">
         <v>780</v>
       </c>
-      <c r="D52" s="121" t="s">
+      <c r="D52" s="117" t="s">
         <v>728</v>
       </c>
-      <c r="E52" s="121"/>
-      <c r="F52" s="121"/>
-      <c r="G52" s="121"/>
-      <c r="H52" s="121"/>
-      <c r="I52" s="121"/>
-      <c r="J52" s="121"/>
-      <c r="K52" s="121"/>
-      <c r="L52" s="121"/>
+      <c r="E52" s="117"/>
+      <c r="F52" s="117"/>
+      <c r="G52" s="117"/>
+      <c r="H52" s="117"/>
+      <c r="I52" s="117"/>
+      <c r="J52" s="117"/>
+      <c r="K52" s="117"/>
+      <c r="L52" s="117"/>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="41" t="s">
@@ -10651,17 +10664,17 @@
       <c r="C53" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D53" s="121" t="s">
+      <c r="D53" s="117" t="s">
         <v>722</v>
       </c>
-      <c r="E53" s="121"/>
-      <c r="F53" s="121"/>
-      <c r="G53" s="121"/>
-      <c r="H53" s="121"/>
-      <c r="I53" s="121"/>
-      <c r="J53" s="121"/>
-      <c r="K53" s="121"/>
-      <c r="L53" s="121"/>
+      <c r="E53" s="117"/>
+      <c r="F53" s="117"/>
+      <c r="G53" s="117"/>
+      <c r="H53" s="117"/>
+      <c r="I53" s="117"/>
+      <c r="J53" s="117"/>
+      <c r="K53" s="117"/>
+      <c r="L53" s="117"/>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="41" t="s">
@@ -10673,17 +10686,17 @@
       <c r="C54" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D54" s="121" t="s">
+      <c r="D54" s="117" t="s">
         <v>723</v>
       </c>
-      <c r="E54" s="121"/>
-      <c r="F54" s="121"/>
-      <c r="G54" s="121"/>
-      <c r="H54" s="121"/>
-      <c r="I54" s="121"/>
-      <c r="J54" s="121"/>
-      <c r="K54" s="121"/>
-      <c r="L54" s="121"/>
+      <c r="E54" s="117"/>
+      <c r="F54" s="117"/>
+      <c r="G54" s="117"/>
+      <c r="H54" s="117"/>
+      <c r="I54" s="117"/>
+      <c r="J54" s="117"/>
+      <c r="K54" s="117"/>
+      <c r="L54" s="117"/>
     </row>
     <row r="55" spans="1:12" ht="37.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="41" t="s">
@@ -10695,17 +10708,17 @@
       <c r="C55" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D55" s="121" t="s">
+      <c r="D55" s="117" t="s">
         <v>777</v>
       </c>
-      <c r="E55" s="121"/>
-      <c r="F55" s="121"/>
-      <c r="G55" s="121"/>
-      <c r="H55" s="121"/>
-      <c r="I55" s="121"/>
-      <c r="J55" s="121"/>
-      <c r="K55" s="121"/>
-      <c r="L55" s="121"/>
+      <c r="E55" s="117"/>
+      <c r="F55" s="117"/>
+      <c r="G55" s="117"/>
+      <c r="H55" s="117"/>
+      <c r="I55" s="117"/>
+      <c r="J55" s="117"/>
+      <c r="K55" s="117"/>
+      <c r="L55" s="117"/>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="41" t="s">
@@ -10717,17 +10730,17 @@
       <c r="C56" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D56" s="121" t="s">
+      <c r="D56" s="117" t="s">
         <v>772</v>
       </c>
-      <c r="E56" s="121"/>
-      <c r="F56" s="121"/>
-      <c r="G56" s="121"/>
-      <c r="H56" s="121"/>
-      <c r="I56" s="121"/>
-      <c r="J56" s="121"/>
-      <c r="K56" s="121"/>
-      <c r="L56" s="121"/>
+      <c r="E56" s="117"/>
+      <c r="F56" s="117"/>
+      <c r="G56" s="117"/>
+      <c r="H56" s="117"/>
+      <c r="I56" s="117"/>
+      <c r="J56" s="117"/>
+      <c r="K56" s="117"/>
+      <c r="L56" s="117"/>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="41" t="s">
@@ -10739,17 +10752,17 @@
       <c r="C57" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D57" s="121" t="s">
+      <c r="D57" s="117" t="s">
         <v>776</v>
       </c>
-      <c r="E57" s="121"/>
-      <c r="F57" s="121"/>
-      <c r="G57" s="121"/>
-      <c r="H57" s="121"/>
-      <c r="I57" s="121"/>
-      <c r="J57" s="121"/>
-      <c r="K57" s="121"/>
-      <c r="L57" s="121"/>
+      <c r="E57" s="117"/>
+      <c r="F57" s="117"/>
+      <c r="G57" s="117"/>
+      <c r="H57" s="117"/>
+      <c r="I57" s="117"/>
+      <c r="J57" s="117"/>
+      <c r="K57" s="117"/>
+      <c r="L57" s="117"/>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="41" t="s">
@@ -10761,17 +10774,17 @@
       <c r="C58" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D58" s="121" t="s">
+      <c r="D58" s="117" t="s">
         <v>752</v>
       </c>
-      <c r="E58" s="121"/>
-      <c r="F58" s="121"/>
-      <c r="G58" s="121"/>
-      <c r="H58" s="121"/>
-      <c r="I58" s="121"/>
-      <c r="J58" s="121"/>
-      <c r="K58" s="121"/>
-      <c r="L58" s="121"/>
+      <c r="E58" s="117"/>
+      <c r="F58" s="117"/>
+      <c r="G58" s="117"/>
+      <c r="H58" s="117"/>
+      <c r="I58" s="117"/>
+      <c r="J58" s="117"/>
+      <c r="K58" s="117"/>
+      <c r="L58" s="117"/>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="41" t="s">
@@ -10783,17 +10796,17 @@
       <c r="C59" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D59" s="121" t="s">
+      <c r="D59" s="117" t="s">
         <v>713</v>
       </c>
-      <c r="E59" s="121"/>
-      <c r="F59" s="121"/>
-      <c r="G59" s="121"/>
-      <c r="H59" s="121"/>
-      <c r="I59" s="121"/>
-      <c r="J59" s="121"/>
-      <c r="K59" s="121"/>
-      <c r="L59" s="121"/>
+      <c r="E59" s="117"/>
+      <c r="F59" s="117"/>
+      <c r="G59" s="117"/>
+      <c r="H59" s="117"/>
+      <c r="I59" s="117"/>
+      <c r="J59" s="117"/>
+      <c r="K59" s="117"/>
+      <c r="L59" s="117"/>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A60" s="41" t="s">
@@ -10805,17 +10818,17 @@
       <c r="C60" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D60" s="121" t="s">
+      <c r="D60" s="117" t="s">
         <v>749</v>
       </c>
-      <c r="E60" s="121"/>
-      <c r="F60" s="121"/>
-      <c r="G60" s="121"/>
-      <c r="H60" s="121"/>
-      <c r="I60" s="121"/>
-      <c r="J60" s="121"/>
-      <c r="K60" s="121"/>
-      <c r="L60" s="121"/>
+      <c r="E60" s="117"/>
+      <c r="F60" s="117"/>
+      <c r="G60" s="117"/>
+      <c r="H60" s="117"/>
+      <c r="I60" s="117"/>
+      <c r="J60" s="117"/>
+      <c r="K60" s="117"/>
+      <c r="L60" s="117"/>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A61" s="41" t="s">
@@ -10827,17 +10840,17 @@
       <c r="C61" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D61" s="121" t="s">
+      <c r="D61" s="117" t="s">
         <v>745</v>
       </c>
-      <c r="E61" s="121"/>
-      <c r="F61" s="121"/>
-      <c r="G61" s="121"/>
-      <c r="H61" s="121"/>
-      <c r="I61" s="121"/>
-      <c r="J61" s="121"/>
-      <c r="K61" s="121"/>
-      <c r="L61" s="121"/>
+      <c r="E61" s="117"/>
+      <c r="F61" s="117"/>
+      <c r="G61" s="117"/>
+      <c r="H61" s="117"/>
+      <c r="I61" s="117"/>
+      <c r="J61" s="117"/>
+      <c r="K61" s="117"/>
+      <c r="L61" s="117"/>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A62" s="41" t="s">
@@ -10849,17 +10862,17 @@
       <c r="C62" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D62" s="121" t="s">
+      <c r="D62" s="117" t="s">
         <v>756</v>
       </c>
-      <c r="E62" s="121"/>
-      <c r="F62" s="121"/>
-      <c r="G62" s="121"/>
-      <c r="H62" s="121"/>
-      <c r="I62" s="121"/>
-      <c r="J62" s="121"/>
-      <c r="K62" s="121"/>
-      <c r="L62" s="121"/>
+      <c r="E62" s="117"/>
+      <c r="F62" s="117"/>
+      <c r="G62" s="117"/>
+      <c r="H62" s="117"/>
+      <c r="I62" s="117"/>
+      <c r="J62" s="117"/>
+      <c r="K62" s="117"/>
+      <c r="L62" s="117"/>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A63" s="41" t="s">
@@ -10871,17 +10884,17 @@
       <c r="C63" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D63" s="121" t="s">
+      <c r="D63" s="117" t="s">
         <v>754</v>
       </c>
-      <c r="E63" s="121"/>
-      <c r="F63" s="121"/>
-      <c r="G63" s="121"/>
-      <c r="H63" s="121"/>
-      <c r="I63" s="121"/>
-      <c r="J63" s="121"/>
-      <c r="K63" s="121"/>
-      <c r="L63" s="121"/>
+      <c r="E63" s="117"/>
+      <c r="F63" s="117"/>
+      <c r="G63" s="117"/>
+      <c r="H63" s="117"/>
+      <c r="I63" s="117"/>
+      <c r="J63" s="117"/>
+      <c r="K63" s="117"/>
+      <c r="L63" s="117"/>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A64" s="41" t="s">
@@ -10893,17 +10906,17 @@
       <c r="C64" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D64" s="121" t="s">
+      <c r="D64" s="117" t="s">
         <v>713</v>
       </c>
-      <c r="E64" s="121"/>
-      <c r="F64" s="121"/>
-      <c r="G64" s="121"/>
-      <c r="H64" s="121"/>
-      <c r="I64" s="121"/>
-      <c r="J64" s="121"/>
-      <c r="K64" s="121"/>
-      <c r="L64" s="121"/>
+      <c r="E64" s="117"/>
+      <c r="F64" s="117"/>
+      <c r="G64" s="117"/>
+      <c r="H64" s="117"/>
+      <c r="I64" s="117"/>
+      <c r="J64" s="117"/>
+      <c r="K64" s="117"/>
+      <c r="L64" s="117"/>
     </row>
     <row r="65" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="41" t="s">
@@ -10915,17 +10928,17 @@
       <c r="C65" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D65" s="121" t="s">
+      <c r="D65" s="117" t="s">
         <v>760</v>
       </c>
-      <c r="E65" s="121"/>
-      <c r="F65" s="121"/>
-      <c r="G65" s="121"/>
-      <c r="H65" s="121"/>
-      <c r="I65" s="121"/>
-      <c r="J65" s="121"/>
-      <c r="K65" s="121"/>
-      <c r="L65" s="121"/>
+      <c r="E65" s="117"/>
+      <c r="F65" s="117"/>
+      <c r="G65" s="117"/>
+      <c r="H65" s="117"/>
+      <c r="I65" s="117"/>
+      <c r="J65" s="117"/>
+      <c r="K65" s="117"/>
+      <c r="L65" s="117"/>
     </row>
     <row r="66" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="41" t="s">
@@ -10937,17 +10950,17 @@
       <c r="C66" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D66" s="121" t="s">
+      <c r="D66" s="117" t="s">
         <v>769</v>
       </c>
-      <c r="E66" s="121"/>
-      <c r="F66" s="121"/>
-      <c r="G66" s="121"/>
-      <c r="H66" s="121"/>
-      <c r="I66" s="121"/>
-      <c r="J66" s="121"/>
-      <c r="K66" s="121"/>
-      <c r="L66" s="121"/>
+      <c r="E66" s="117"/>
+      <c r="F66" s="117"/>
+      <c r="G66" s="117"/>
+      <c r="H66" s="117"/>
+      <c r="I66" s="117"/>
+      <c r="J66" s="117"/>
+      <c r="K66" s="117"/>
+      <c r="L66" s="117"/>
     </row>
     <row r="67" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="41" t="s">
@@ -10959,17 +10972,17 @@
       <c r="C67" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D67" s="121" t="s">
+      <c r="D67" s="117" t="s">
         <v>284</v>
       </c>
-      <c r="E67" s="121"/>
-      <c r="F67" s="121"/>
-      <c r="G67" s="121"/>
-      <c r="H67" s="121"/>
-      <c r="I67" s="121"/>
-      <c r="J67" s="121"/>
-      <c r="K67" s="121"/>
-      <c r="L67" s="121"/>
+      <c r="E67" s="117"/>
+      <c r="F67" s="117"/>
+      <c r="G67" s="117"/>
+      <c r="H67" s="117"/>
+      <c r="I67" s="117"/>
+      <c r="J67" s="117"/>
+      <c r="K67" s="117"/>
+      <c r="L67" s="117"/>
     </row>
     <row r="68" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="41" t="s">
@@ -10981,17 +10994,17 @@
       <c r="C68" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D68" s="121" t="s">
+      <c r="D68" s="117" t="s">
         <v>717</v>
       </c>
-      <c r="E68" s="121"/>
-      <c r="F68" s="121"/>
-      <c r="G68" s="121"/>
-      <c r="H68" s="121"/>
-      <c r="I68" s="121"/>
-      <c r="J68" s="121"/>
-      <c r="K68" s="121"/>
-      <c r="L68" s="121"/>
+      <c r="E68" s="117"/>
+      <c r="F68" s="117"/>
+      <c r="G68" s="117"/>
+      <c r="H68" s="117"/>
+      <c r="I68" s="117"/>
+      <c r="J68" s="117"/>
+      <c r="K68" s="117"/>
+      <c r="L68" s="117"/>
     </row>
     <row r="69" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="41" t="s">
@@ -11003,17 +11016,17 @@
       <c r="C69" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D69" s="121" t="s">
+      <c r="D69" s="117" t="s">
         <v>744</v>
       </c>
-      <c r="E69" s="121"/>
-      <c r="F69" s="121"/>
-      <c r="G69" s="121"/>
-      <c r="H69" s="121"/>
-      <c r="I69" s="121"/>
-      <c r="J69" s="121"/>
-      <c r="K69" s="121"/>
-      <c r="L69" s="121"/>
+      <c r="E69" s="117"/>
+      <c r="F69" s="117"/>
+      <c r="G69" s="117"/>
+      <c r="H69" s="117"/>
+      <c r="I69" s="117"/>
+      <c r="J69" s="117"/>
+      <c r="K69" s="117"/>
+      <c r="L69" s="117"/>
     </row>
     <row r="70" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="41" t="s">
@@ -11025,17 +11038,17 @@
       <c r="C70" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D70" s="121" t="s">
+      <c r="D70" s="117" t="s">
         <v>717</v>
       </c>
-      <c r="E70" s="121"/>
-      <c r="F70" s="121"/>
-      <c r="G70" s="121"/>
-      <c r="H70" s="121"/>
-      <c r="I70" s="121"/>
-      <c r="J70" s="121"/>
-      <c r="K70" s="121"/>
-      <c r="L70" s="121"/>
+      <c r="E70" s="117"/>
+      <c r="F70" s="117"/>
+      <c r="G70" s="117"/>
+      <c r="H70" s="117"/>
+      <c r="I70" s="117"/>
+      <c r="J70" s="117"/>
+      <c r="K70" s="117"/>
+      <c r="L70" s="117"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" s="41" t="s">
@@ -11047,17 +11060,17 @@
       <c r="C71" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D71" s="121" t="s">
+      <c r="D71" s="117" t="s">
         <v>709</v>
       </c>
-      <c r="E71" s="121"/>
-      <c r="F71" s="121"/>
-      <c r="G71" s="121"/>
-      <c r="H71" s="121"/>
-      <c r="I71" s="121"/>
-      <c r="J71" s="121"/>
-      <c r="K71" s="121"/>
-      <c r="L71" s="121"/>
+      <c r="E71" s="117"/>
+      <c r="F71" s="117"/>
+      <c r="G71" s="117"/>
+      <c r="H71" s="117"/>
+      <c r="I71" s="117"/>
+      <c r="J71" s="117"/>
+      <c r="K71" s="117"/>
+      <c r="L71" s="117"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" s="41" t="s">
@@ -11069,17 +11082,17 @@
       <c r="C72" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D72" s="121" t="s">
+      <c r="D72" s="117" t="s">
         <v>754</v>
       </c>
-      <c r="E72" s="121"/>
-      <c r="F72" s="121"/>
-      <c r="G72" s="121"/>
-      <c r="H72" s="121"/>
-      <c r="I72" s="121"/>
-      <c r="J72" s="121"/>
-      <c r="K72" s="121"/>
-      <c r="L72" s="121"/>
+      <c r="E72" s="117"/>
+      <c r="F72" s="117"/>
+      <c r="G72" s="117"/>
+      <c r="H72" s="117"/>
+      <c r="I72" s="117"/>
+      <c r="J72" s="117"/>
+      <c r="K72" s="117"/>
+      <c r="L72" s="117"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" s="41" t="s">
@@ -11091,17 +11104,17 @@
       <c r="C73" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D73" s="121" t="s">
+      <c r="D73" s="117" t="s">
         <v>758</v>
       </c>
-      <c r="E73" s="121"/>
-      <c r="F73" s="121"/>
-      <c r="G73" s="121"/>
-      <c r="H73" s="121"/>
-      <c r="I73" s="121"/>
-      <c r="J73" s="121"/>
-      <c r="K73" s="121"/>
-      <c r="L73" s="121"/>
+      <c r="E73" s="117"/>
+      <c r="F73" s="117"/>
+      <c r="G73" s="117"/>
+      <c r="H73" s="117"/>
+      <c r="I73" s="117"/>
+      <c r="J73" s="117"/>
+      <c r="K73" s="117"/>
+      <c r="L73" s="117"/>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" s="41" t="s">
@@ -11113,17 +11126,17 @@
       <c r="C74" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D74" s="121" t="s">
+      <c r="D74" s="117" t="s">
         <v>717</v>
       </c>
-      <c r="E74" s="121"/>
-      <c r="F74" s="121"/>
-      <c r="G74" s="121"/>
-      <c r="H74" s="121"/>
-      <c r="I74" s="121"/>
-      <c r="J74" s="121"/>
-      <c r="K74" s="121"/>
-      <c r="L74" s="121"/>
+      <c r="E74" s="117"/>
+      <c r="F74" s="117"/>
+      <c r="G74" s="117"/>
+      <c r="H74" s="117"/>
+      <c r="I74" s="117"/>
+      <c r="J74" s="117"/>
+      <c r="K74" s="117"/>
+      <c r="L74" s="117"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" s="41" t="s">
@@ -11135,17 +11148,17 @@
       <c r="C75" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D75" s="121" t="s">
+      <c r="D75" s="117" t="s">
         <v>787</v>
       </c>
-      <c r="E75" s="121"/>
-      <c r="F75" s="121"/>
-      <c r="G75" s="121"/>
-      <c r="H75" s="121"/>
-      <c r="I75" s="121"/>
-      <c r="J75" s="121"/>
-      <c r="K75" s="121"/>
-      <c r="L75" s="121"/>
+      <c r="E75" s="117"/>
+      <c r="F75" s="117"/>
+      <c r="G75" s="117"/>
+      <c r="H75" s="117"/>
+      <c r="I75" s="117"/>
+      <c r="J75" s="117"/>
+      <c r="K75" s="117"/>
+      <c r="L75" s="117"/>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" s="41" t="s">
@@ -11157,17 +11170,17 @@
       <c r="C76" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D76" s="121" t="s">
+      <c r="D76" s="117" t="s">
         <v>788</v>
       </c>
-      <c r="E76" s="121"/>
-      <c r="F76" s="121"/>
-      <c r="G76" s="121"/>
-      <c r="H76" s="121"/>
-      <c r="I76" s="121"/>
-      <c r="J76" s="121"/>
-      <c r="K76" s="121"/>
-      <c r="L76" s="121"/>
+      <c r="E76" s="117"/>
+      <c r="F76" s="117"/>
+      <c r="G76" s="117"/>
+      <c r="H76" s="117"/>
+      <c r="I76" s="117"/>
+      <c r="J76" s="117"/>
+      <c r="K76" s="117"/>
+      <c r="L76" s="117"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" s="41" t="s">
@@ -11179,17 +11192,17 @@
       <c r="C77" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D77" s="121" t="s">
+      <c r="D77" s="117" t="s">
         <v>747</v>
       </c>
-      <c r="E77" s="121"/>
-      <c r="F77" s="121"/>
-      <c r="G77" s="121"/>
-      <c r="H77" s="121"/>
-      <c r="I77" s="121"/>
-      <c r="J77" s="121"/>
-      <c r="K77" s="121"/>
-      <c r="L77" s="121"/>
+      <c r="E77" s="117"/>
+      <c r="F77" s="117"/>
+      <c r="G77" s="117"/>
+      <c r="H77" s="117"/>
+      <c r="I77" s="117"/>
+      <c r="J77" s="117"/>
+      <c r="K77" s="117"/>
+      <c r="L77" s="117"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" s="41" t="s">
@@ -11201,17 +11214,17 @@
       <c r="C78" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D78" s="121" t="s">
+      <c r="D78" s="117" t="s">
         <v>763</v>
       </c>
-      <c r="E78" s="121"/>
-      <c r="F78" s="121"/>
-      <c r="G78" s="121"/>
-      <c r="H78" s="121"/>
-      <c r="I78" s="121"/>
-      <c r="J78" s="121"/>
-      <c r="K78" s="121"/>
-      <c r="L78" s="121"/>
+      <c r="E78" s="117"/>
+      <c r="F78" s="117"/>
+      <c r="G78" s="117"/>
+      <c r="H78" s="117"/>
+      <c r="I78" s="117"/>
+      <c r="J78" s="117"/>
+      <c r="K78" s="117"/>
+      <c r="L78" s="117"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" s="41" t="s">
@@ -11223,17 +11236,17 @@
       <c r="C79" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D79" s="121" t="s">
+      <c r="D79" s="117" t="s">
         <v>720</v>
       </c>
-      <c r="E79" s="121"/>
-      <c r="F79" s="121"/>
-      <c r="G79" s="121"/>
-      <c r="H79" s="121"/>
-      <c r="I79" s="121"/>
-      <c r="J79" s="121"/>
-      <c r="K79" s="121"/>
-      <c r="L79" s="121"/>
+      <c r="E79" s="117"/>
+      <c r="F79" s="117"/>
+      <c r="G79" s="117"/>
+      <c r="H79" s="117"/>
+      <c r="I79" s="117"/>
+      <c r="J79" s="117"/>
+      <c r="K79" s="117"/>
+      <c r="L79" s="117"/>
     </row>
     <row r="80" spans="1:12" ht="31.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="41" t="s">
@@ -11245,17 +11258,17 @@
       <c r="C80" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D80" s="121" t="s">
+      <c r="D80" s="117" t="s">
         <v>779</v>
       </c>
-      <c r="E80" s="121"/>
-      <c r="F80" s="121"/>
-      <c r="G80" s="121"/>
-      <c r="H80" s="121"/>
-      <c r="I80" s="121"/>
-      <c r="J80" s="121"/>
-      <c r="K80" s="121"/>
-      <c r="L80" s="121"/>
+      <c r="E80" s="117"/>
+      <c r="F80" s="117"/>
+      <c r="G80" s="117"/>
+      <c r="H80" s="117"/>
+      <c r="I80" s="117"/>
+      <c r="J80" s="117"/>
+      <c r="K80" s="117"/>
+      <c r="L80" s="117"/>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" s="41" t="s">
@@ -11267,17 +11280,17 @@
       <c r="C81" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D81" s="121" t="s">
+      <c r="D81" s="117" t="s">
         <v>716</v>
       </c>
-      <c r="E81" s="121"/>
-      <c r="F81" s="121"/>
-      <c r="G81" s="121"/>
-      <c r="H81" s="121"/>
-      <c r="I81" s="121"/>
-      <c r="J81" s="121"/>
-      <c r="K81" s="121"/>
-      <c r="L81" s="121"/>
+      <c r="E81" s="117"/>
+      <c r="F81" s="117"/>
+      <c r="G81" s="117"/>
+      <c r="H81" s="117"/>
+      <c r="I81" s="117"/>
+      <c r="J81" s="117"/>
+      <c r="K81" s="117"/>
+      <c r="L81" s="117"/>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" s="41" t="s">
@@ -11289,17 +11302,17 @@
       <c r="C82" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D82" s="121" t="s">
+      <c r="D82" s="117" t="s">
         <v>746</v>
       </c>
-      <c r="E82" s="121"/>
-      <c r="F82" s="121"/>
-      <c r="G82" s="121"/>
-      <c r="H82" s="121"/>
-      <c r="I82" s="121"/>
-      <c r="J82" s="121"/>
-      <c r="K82" s="121"/>
-      <c r="L82" s="121"/>
+      <c r="E82" s="117"/>
+      <c r="F82" s="117"/>
+      <c r="G82" s="117"/>
+      <c r="H82" s="117"/>
+      <c r="I82" s="117"/>
+      <c r="J82" s="117"/>
+      <c r="K82" s="117"/>
+      <c r="L82" s="117"/>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" s="41" t="s">
@@ -11311,17 +11324,17 @@
       <c r="C83" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D83" s="121" t="s">
+      <c r="D83" s="117" t="s">
         <v>717</v>
       </c>
-      <c r="E83" s="121"/>
-      <c r="F83" s="121"/>
-      <c r="G83" s="121"/>
-      <c r="H83" s="121"/>
-      <c r="I83" s="121"/>
-      <c r="J83" s="121"/>
-      <c r="K83" s="121"/>
-      <c r="L83" s="121"/>
+      <c r="E83" s="117"/>
+      <c r="F83" s="117"/>
+      <c r="G83" s="117"/>
+      <c r="H83" s="117"/>
+      <c r="I83" s="117"/>
+      <c r="J83" s="117"/>
+      <c r="K83" s="117"/>
+      <c r="L83" s="117"/>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" s="41" t="s">
@@ -11333,17 +11346,17 @@
       <c r="C84" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D84" s="121" t="s">
+      <c r="D84" s="117" t="s">
         <v>750</v>
       </c>
-      <c r="E84" s="121"/>
-      <c r="F84" s="121"/>
-      <c r="G84" s="121"/>
-      <c r="H84" s="121"/>
-      <c r="I84" s="121"/>
-      <c r="J84" s="121"/>
-      <c r="K84" s="121"/>
-      <c r="L84" s="121"/>
+      <c r="E84" s="117"/>
+      <c r="F84" s="117"/>
+      <c r="G84" s="117"/>
+      <c r="H84" s="117"/>
+      <c r="I84" s="117"/>
+      <c r="J84" s="117"/>
+      <c r="K84" s="117"/>
+      <c r="L84" s="117"/>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" s="41" t="s">
@@ -11355,17 +11368,17 @@
       <c r="C85" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D85" s="121" t="s">
+      <c r="D85" s="117" t="s">
         <v>771</v>
       </c>
-      <c r="E85" s="121"/>
-      <c r="F85" s="121"/>
-      <c r="G85" s="121"/>
-      <c r="H85" s="121"/>
-      <c r="I85" s="121"/>
-      <c r="J85" s="121"/>
-      <c r="K85" s="121"/>
-      <c r="L85" s="121"/>
+      <c r="E85" s="117"/>
+      <c r="F85" s="117"/>
+      <c r="G85" s="117"/>
+      <c r="H85" s="117"/>
+      <c r="I85" s="117"/>
+      <c r="J85" s="117"/>
+      <c r="K85" s="117"/>
+      <c r="L85" s="117"/>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" s="41" t="s">
@@ -11377,17 +11390,17 @@
       <c r="C86" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D86" s="121" t="s">
+      <c r="D86" s="117" t="s">
         <v>715</v>
       </c>
-      <c r="E86" s="121"/>
-      <c r="F86" s="121"/>
-      <c r="G86" s="121"/>
-      <c r="H86" s="121"/>
-      <c r="I86" s="121"/>
-      <c r="J86" s="121"/>
-      <c r="K86" s="121"/>
-      <c r="L86" s="121"/>
+      <c r="E86" s="117"/>
+      <c r="F86" s="117"/>
+      <c r="G86" s="117"/>
+      <c r="H86" s="117"/>
+      <c r="I86" s="117"/>
+      <c r="J86" s="117"/>
+      <c r="K86" s="117"/>
+      <c r="L86" s="117"/>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" s="41" t="s">
@@ -11399,17 +11412,17 @@
       <c r="C87" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D87" s="121" t="s">
+      <c r="D87" s="117" t="s">
         <v>727</v>
       </c>
-      <c r="E87" s="121"/>
-      <c r="F87" s="121"/>
-      <c r="G87" s="121"/>
-      <c r="H87" s="121"/>
-      <c r="I87" s="121"/>
-      <c r="J87" s="121"/>
-      <c r="K87" s="121"/>
-      <c r="L87" s="121"/>
+      <c r="E87" s="117"/>
+      <c r="F87" s="117"/>
+      <c r="G87" s="117"/>
+      <c r="H87" s="117"/>
+      <c r="I87" s="117"/>
+      <c r="J87" s="117"/>
+      <c r="K87" s="117"/>
+      <c r="L87" s="117"/>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" s="41" t="s">
@@ -11421,17 +11434,17 @@
       <c r="C88" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D88" s="121" t="s">
+      <c r="D88" s="117" t="s">
         <v>767</v>
       </c>
-      <c r="E88" s="121"/>
-      <c r="F88" s="121"/>
-      <c r="G88" s="121"/>
-      <c r="H88" s="121"/>
-      <c r="I88" s="121"/>
-      <c r="J88" s="121"/>
-      <c r="K88" s="121"/>
-      <c r="L88" s="121"/>
+      <c r="E88" s="117"/>
+      <c r="F88" s="117"/>
+      <c r="G88" s="117"/>
+      <c r="H88" s="117"/>
+      <c r="I88" s="117"/>
+      <c r="J88" s="117"/>
+      <c r="K88" s="117"/>
+      <c r="L88" s="117"/>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" s="41" t="s">
@@ -11443,17 +11456,17 @@
       <c r="C89" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D89" s="121" t="s">
+      <c r="D89" s="117" t="s">
         <v>730</v>
       </c>
-      <c r="E89" s="121"/>
-      <c r="F89" s="121"/>
-      <c r="G89" s="121"/>
-      <c r="H89" s="121"/>
-      <c r="I89" s="121"/>
-      <c r="J89" s="121"/>
-      <c r="K89" s="121"/>
-      <c r="L89" s="121"/>
+      <c r="E89" s="117"/>
+      <c r="F89" s="117"/>
+      <c r="G89" s="117"/>
+      <c r="H89" s="117"/>
+      <c r="I89" s="117"/>
+      <c r="J89" s="117"/>
+      <c r="K89" s="117"/>
+      <c r="L89" s="117"/>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" s="41" t="s">
@@ -11465,17 +11478,17 @@
       <c r="C90" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D90" s="121" t="s">
+      <c r="D90" s="117" t="s">
         <v>732</v>
       </c>
-      <c r="E90" s="121"/>
-      <c r="F90" s="121"/>
-      <c r="G90" s="121"/>
-      <c r="H90" s="121"/>
-      <c r="I90" s="121"/>
-      <c r="J90" s="121"/>
-      <c r="K90" s="121"/>
-      <c r="L90" s="121"/>
+      <c r="E90" s="117"/>
+      <c r="F90" s="117"/>
+      <c r="G90" s="117"/>
+      <c r="H90" s="117"/>
+      <c r="I90" s="117"/>
+      <c r="J90" s="117"/>
+      <c r="K90" s="117"/>
+      <c r="L90" s="117"/>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" s="41" t="s">
@@ -11487,17 +11500,17 @@
       <c r="C91" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D91" s="121" t="s">
+      <c r="D91" s="117" t="s">
         <v>774</v>
       </c>
-      <c r="E91" s="121"/>
-      <c r="F91" s="121"/>
-      <c r="G91" s="121"/>
-      <c r="H91" s="121"/>
-      <c r="I91" s="121"/>
-      <c r="J91" s="121"/>
-      <c r="K91" s="121"/>
-      <c r="L91" s="121"/>
+      <c r="E91" s="117"/>
+      <c r="F91" s="117"/>
+      <c r="G91" s="117"/>
+      <c r="H91" s="117"/>
+      <c r="I91" s="117"/>
+      <c r="J91" s="117"/>
+      <c r="K91" s="117"/>
+      <c r="L91" s="117"/>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" s="41" t="s">
@@ -11509,17 +11522,17 @@
       <c r="C92" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D92" s="121" t="s">
+      <c r="D92" s="117" t="s">
         <v>711</v>
       </c>
-      <c r="E92" s="121"/>
-      <c r="F92" s="121"/>
-      <c r="G92" s="121"/>
-      <c r="H92" s="121"/>
-      <c r="I92" s="121"/>
-      <c r="J92" s="121"/>
-      <c r="K92" s="121"/>
-      <c r="L92" s="121"/>
+      <c r="E92" s="117"/>
+      <c r="F92" s="117"/>
+      <c r="G92" s="117"/>
+      <c r="H92" s="117"/>
+      <c r="I92" s="117"/>
+      <c r="J92" s="117"/>
+      <c r="K92" s="117"/>
+      <c r="L92" s="117"/>
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" s="41" t="s">
@@ -11531,28 +11544,64 @@
       <c r="C93" s="41" t="s">
         <v>713</v>
       </c>
-      <c r="D93" s="121" t="s">
+      <c r="D93" s="117" t="s">
         <v>765</v>
       </c>
-      <c r="E93" s="121"/>
-      <c r="F93" s="121"/>
-      <c r="G93" s="121"/>
-      <c r="H93" s="121"/>
-      <c r="I93" s="121"/>
-      <c r="J93" s="121"/>
-      <c r="K93" s="121"/>
-      <c r="L93" s="121"/>
+      <c r="E93" s="117"/>
+      <c r="F93" s="117"/>
+      <c r="G93" s="117"/>
+      <c r="H93" s="117"/>
+      <c r="I93" s="117"/>
+      <c r="J93" s="117"/>
+      <c r="K93" s="117"/>
+      <c r="L93" s="117"/>
     </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A46:D93">
     <sortCondition ref="A46:A93"/>
   </sortState>
   <mergeCells count="61">
-    <mergeCell ref="B5:G5"/>
-    <mergeCell ref="B6:G6"/>
-    <mergeCell ref="B7:G7"/>
-    <mergeCell ref="B8:G8"/>
-    <mergeCell ref="D16:L16"/>
+    <mergeCell ref="D82:L82"/>
+    <mergeCell ref="D81:L81"/>
+    <mergeCell ref="D80:L80"/>
+    <mergeCell ref="D93:L93"/>
+    <mergeCell ref="D92:L92"/>
+    <mergeCell ref="D91:L91"/>
+    <mergeCell ref="D90:L90"/>
+    <mergeCell ref="D89:L89"/>
+    <mergeCell ref="D88:L88"/>
+    <mergeCell ref="D87:L87"/>
+    <mergeCell ref="D86:L86"/>
+    <mergeCell ref="D85:L85"/>
+    <mergeCell ref="D84:L84"/>
+    <mergeCell ref="D83:L83"/>
+    <mergeCell ref="D73:L73"/>
+    <mergeCell ref="D72:L72"/>
+    <mergeCell ref="D71:L71"/>
+    <mergeCell ref="D70:L70"/>
+    <mergeCell ref="D79:L79"/>
+    <mergeCell ref="D78:L78"/>
+    <mergeCell ref="D76:L76"/>
+    <mergeCell ref="D77:L77"/>
+    <mergeCell ref="D75:L75"/>
+    <mergeCell ref="D74:L74"/>
+    <mergeCell ref="D64:L64"/>
+    <mergeCell ref="D63:L63"/>
+    <mergeCell ref="D62:L62"/>
+    <mergeCell ref="D61:L61"/>
+    <mergeCell ref="D60:L60"/>
+    <mergeCell ref="D69:L69"/>
+    <mergeCell ref="D68:L68"/>
+    <mergeCell ref="D67:L67"/>
+    <mergeCell ref="D66:L66"/>
+    <mergeCell ref="D65:L65"/>
+    <mergeCell ref="D53:L53"/>
+    <mergeCell ref="D59:L59"/>
+    <mergeCell ref="D58:L58"/>
+    <mergeCell ref="D57:L57"/>
+    <mergeCell ref="D56:L56"/>
+    <mergeCell ref="D55:L55"/>
+    <mergeCell ref="D54:L54"/>
     <mergeCell ref="D52:L52"/>
     <mergeCell ref="D15:L15"/>
     <mergeCell ref="A13:B13"/>
@@ -11567,48 +11616,12 @@
     <mergeCell ref="D47:L47"/>
     <mergeCell ref="D50:L50"/>
     <mergeCell ref="D51:L51"/>
-    <mergeCell ref="D53:L53"/>
-    <mergeCell ref="D59:L59"/>
-    <mergeCell ref="D58:L58"/>
-    <mergeCell ref="D57:L57"/>
-    <mergeCell ref="D56:L56"/>
-    <mergeCell ref="D55:L55"/>
-    <mergeCell ref="D54:L54"/>
-    <mergeCell ref="D69:L69"/>
-    <mergeCell ref="D68:L68"/>
-    <mergeCell ref="D67:L67"/>
-    <mergeCell ref="D66:L66"/>
-    <mergeCell ref="D65:L65"/>
-    <mergeCell ref="D64:L64"/>
-    <mergeCell ref="D63:L63"/>
-    <mergeCell ref="D62:L62"/>
-    <mergeCell ref="D61:L61"/>
-    <mergeCell ref="D60:L60"/>
-    <mergeCell ref="D73:L73"/>
-    <mergeCell ref="D72:L72"/>
-    <mergeCell ref="D71:L71"/>
-    <mergeCell ref="D70:L70"/>
-    <mergeCell ref="D79:L79"/>
-    <mergeCell ref="D78:L78"/>
-    <mergeCell ref="D76:L76"/>
-    <mergeCell ref="D77:L77"/>
-    <mergeCell ref="D75:L75"/>
     <mergeCell ref="A37:C43"/>
-    <mergeCell ref="D82:L82"/>
-    <mergeCell ref="D81:L81"/>
-    <mergeCell ref="D80:L80"/>
-    <mergeCell ref="D93:L93"/>
-    <mergeCell ref="D92:L92"/>
-    <mergeCell ref="D91:L91"/>
-    <mergeCell ref="D90:L90"/>
-    <mergeCell ref="D89:L89"/>
-    <mergeCell ref="D88:L88"/>
-    <mergeCell ref="D87:L87"/>
-    <mergeCell ref="D86:L86"/>
-    <mergeCell ref="D85:L85"/>
-    <mergeCell ref="D84:L84"/>
-    <mergeCell ref="D83:L83"/>
-    <mergeCell ref="D74:L74"/>
+    <mergeCell ref="B5:G5"/>
+    <mergeCell ref="B6:G6"/>
+    <mergeCell ref="B7:G7"/>
+    <mergeCell ref="B8:G8"/>
+    <mergeCell ref="D16:L16"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -11634,7 +11647,7 @@
     <col min="11" max="11" width="14.42578125" customWidth="1"/>
     <col min="12" max="12" width="17.85546875" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="17.85546875" customWidth="1"/>
-    <col min="14" max="14" width="47.7109375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="19.5703125" customWidth="1"/>
     <col min="16" max="16" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -11679,10 +11692,10 @@
       <c r="A5" s="60"/>
       <c r="B5" s="60"/>
       <c r="C5" s="60"/>
-      <c r="D5" s="141" t="s">
+      <c r="D5" s="138" t="s">
         <v>95</v>
       </c>
-      <c r="E5" s="141"/>
+      <c r="E5" s="138"/>
       <c r="F5" s="60"/>
       <c r="G5" s="60"/>
       <c r="H5" s="60"/>
@@ -36572,7 +36585,7 @@
         <v>15</v>
       </c>
       <c r="L583" s="65">
-        <f t="shared" ref="L583:L646" si="9">(K583/$P$7)*100</f>
+        <f t="shared" ref="L583:L628" si="9">(K583/$P$7)*100</f>
         <v>0.28462998102466791</v>
       </c>
       <c r="M583" s="1" t="s">
@@ -38560,36 +38573,36 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A1" s="142" t="s">
+      <c r="A1" s="139" t="s">
         <v>658</v>
       </c>
-      <c r="B1" s="142"/>
-      <c r="C1" s="142"/>
-      <c r="D1" s="142"/>
-      <c r="E1" s="142"/>
-      <c r="F1" s="142"/>
-      <c r="G1" s="142"/>
-      <c r="H1" s="142"/>
-      <c r="I1" s="142"/>
-      <c r="J1" s="142"/>
-      <c r="K1" s="142"/>
-      <c r="L1" s="142"/>
-      <c r="M1" s="142"/>
+      <c r="B1" s="139"/>
+      <c r="C1" s="139"/>
+      <c r="D1" s="139"/>
+      <c r="E1" s="139"/>
+      <c r="F1" s="139"/>
+      <c r="G1" s="139"/>
+      <c r="H1" s="139"/>
+      <c r="I1" s="139"/>
+      <c r="J1" s="139"/>
+      <c r="K1" s="139"/>
+      <c r="L1" s="139"/>
+      <c r="M1" s="139"/>
     </row>
     <row r="2" spans="1:13" ht="18.600000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="142"/>
-      <c r="B2" s="142"/>
-      <c r="C2" s="142"/>
-      <c r="D2" s="142"/>
-      <c r="E2" s="142"/>
-      <c r="F2" s="142"/>
-      <c r="G2" s="142"/>
-      <c r="H2" s="142"/>
-      <c r="I2" s="142"/>
-      <c r="J2" s="142"/>
-      <c r="K2" s="142"/>
-      <c r="L2" s="142"/>
-      <c r="M2" s="142"/>
+      <c r="A2" s="139"/>
+      <c r="B2" s="139"/>
+      <c r="C2" s="139"/>
+      <c r="D2" s="139"/>
+      <c r="E2" s="139"/>
+      <c r="F2" s="139"/>
+      <c r="G2" s="139"/>
+      <c r="H2" s="139"/>
+      <c r="I2" s="139"/>
+      <c r="J2" s="139"/>
+      <c r="K2" s="139"/>
+      <c r="L2" s="139"/>
+      <c r="M2" s="139"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="69" t="s">
@@ -42125,23 +42138,23 @@
       <c r="D4" s="4"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="126" t="s">
         <v>659</v>
       </c>
-      <c r="B5" s="117"/>
-      <c r="C5" s="117"/>
-      <c r="D5" s="117"/>
-      <c r="E5" s="117"/>
+      <c r="B5" s="126"/>
+      <c r="C5" s="126"/>
+      <c r="D5" s="126"/>
+      <c r="E5" s="126"/>
       <c r="F5" s="30"/>
       <c r="G5" s="30"/>
-      <c r="H5" s="117" t="s">
+      <c r="H5" s="126" t="s">
         <v>660</v>
       </c>
-      <c r="I5" s="117"/>
-      <c r="J5" s="117"/>
-      <c r="K5" s="117"/>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
+      <c r="I5" s="126"/>
+      <c r="J5" s="126"/>
+      <c r="K5" s="126"/>
+      <c r="L5" s="126"/>
+      <c r="M5" s="126"/>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="30"/>
@@ -42171,15 +42184,15 @@
       <c r="H8" s="34"/>
     </row>
     <row r="9" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="148" t="s">
+      <c r="A9" s="141" t="s">
         <v>528</v>
       </c>
-      <c r="B9" s="150" t="s">
+      <c r="B9" s="140" t="s">
         <v>529</v>
       </c>
-      <c r="C9" s="150"/>
-      <c r="D9" s="150"/>
-      <c r="E9" s="150"/>
+      <c r="C9" s="140"/>
+      <c r="D9" s="140"/>
+      <c r="E9" s="140"/>
       <c r="F9" s="30"/>
       <c r="G9" s="30"/>
       <c r="H9" s="143" t="s">
@@ -42192,7 +42205,7 @@
       <c r="M9" s="143"/>
     </row>
     <row r="10" spans="1:13" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="149"/>
+      <c r="A10" s="142"/>
       <c r="B10" s="5" t="s">
         <v>530</v>
       </c>
@@ -42334,7 +42347,7 @@
       </c>
       <c r="F15" s="3"/>
       <c r="G15" s="3"/>
-      <c r="H15" s="148" t="s">
+      <c r="H15" s="141" t="s">
         <v>528</v>
       </c>
       <c r="I15" s="145" t="s">
@@ -42363,7 +42376,7 @@
       </c>
       <c r="F16" s="3"/>
       <c r="G16" s="3"/>
-      <c r="H16" s="149"/>
+      <c r="H16" s="142"/>
       <c r="I16" s="16" t="s">
         <v>598</v>
       </c>
@@ -42873,19 +42886,19 @@
       </c>
     </row>
     <row r="6" spans="1:27" ht="30" x14ac:dyDescent="0.25">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="151" t="s">
         <v>548</v>
       </c>
-      <c r="B6" s="153" t="s">
+      <c r="B6" s="151" t="s">
         <v>29</v>
       </c>
-      <c r="C6" s="151" t="s">
+      <c r="C6" s="149" t="s">
         <v>549</v>
       </c>
-      <c r="D6" s="151" t="s">
+      <c r="D6" s="149" t="s">
         <v>550</v>
       </c>
-      <c r="E6" s="151" t="s">
+      <c r="E6" s="149" t="s">
         <v>482</v>
       </c>
       <c r="F6" s="89" t="s">
@@ -42956,11 +42969,11 @@
       </c>
     </row>
     <row r="7" spans="1:27" x14ac:dyDescent="0.25">
-      <c r="A7" s="154"/>
-      <c r="B7" s="154"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
+      <c r="A7" s="152"/>
+      <c r="B7" s="152"/>
+      <c r="C7" s="150"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="150"/>
       <c r="F7" s="88" t="s">
         <v>572</v>
       </c>
@@ -43671,7 +43684,7 @@
       <c r="A19" s="4"/>
     </row>
     <row r="20" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A20" s="123" t="s">
+      <c r="A20" s="148" t="s">
         <v>794</v>
       </c>
       <c r="B20" s="89" t="s">
@@ -43718,7 +43731,7 @@
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="123"/>
+      <c r="A21" s="148"/>
       <c r="B21" s="88" t="s">
         <v>577</v>
       </c>
@@ -43962,7 +43975,7 @@
       <c r="O25" s="112"/>
     </row>
     <row r="26" spans="1:15" ht="30" x14ac:dyDescent="0.25">
-      <c r="A26" s="123" t="s">
+      <c r="A26" s="148" t="s">
         <v>794</v>
       </c>
       <c r="B26" s="89" t="s">
@@ -44009,7 +44022,7 @@
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A27" s="123"/>
+      <c r="A27" s="148"/>
       <c r="B27" s="88" t="s">
         <v>577</v>
       </c>
@@ -44491,13 +44504,13 @@
       <c r="O4" s="79">
         <v>3.8759999999999994</v>
       </c>
-      <c r="P4" s="158">
+      <c r="P4" s="156">
         <v>1.8531575755990095</v>
       </c>
-      <c r="Q4" s="158">
+      <c r="Q4" s="156">
         <v>1.1114999999999999</v>
       </c>
-      <c r="R4" s="155">
+      <c r="R4" s="153">
         <f>+ AVERAGE(O4:O15)</f>
         <v>1.4629999999999999</v>
       </c>
@@ -44542,9 +44555,9 @@
       <c r="O5" s="79">
         <v>0.45600000000000041</v>
       </c>
-      <c r="P5" s="158"/>
-      <c r="Q5" s="158"/>
-      <c r="R5" s="156"/>
+      <c r="P5" s="156"/>
+      <c r="Q5" s="156"/>
+      <c r="R5" s="154"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A6" s="13">
@@ -44586,9 +44599,9 @@
       <c r="O6" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P6" s="158"/>
-      <c r="Q6" s="158"/>
-      <c r="R6" s="156"/>
+      <c r="P6" s="156"/>
+      <c r="Q6" s="156"/>
+      <c r="R6" s="154"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A7" s="13">
@@ -44630,9 +44643,9 @@
       <c r="O7" s="79">
         <v>0</v>
       </c>
-      <c r="P7" s="158"/>
-      <c r="Q7" s="158"/>
-      <c r="R7" s="156"/>
+      <c r="P7" s="156"/>
+      <c r="Q7" s="156"/>
+      <c r="R7" s="154"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A8" s="13">
@@ -44674,13 +44687,13 @@
       <c r="O8" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P8" s="158">
+      <c r="P8" s="156">
         <v>0.40971331440410846</v>
       </c>
-      <c r="Q8" s="158">
+      <c r="Q8" s="156">
         <v>0.48450000000000004</v>
       </c>
-      <c r="R8" s="156"/>
+      <c r="R8" s="154"/>
     </row>
     <row r="9" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A9" s="13">
@@ -44722,9 +44735,9 @@
       <c r="O9" s="79">
         <v>1.026</v>
       </c>
-      <c r="P9" s="158"/>
-      <c r="Q9" s="158"/>
-      <c r="R9" s="156"/>
+      <c r="P9" s="156"/>
+      <c r="Q9" s="156"/>
+      <c r="R9" s="154"/>
     </row>
     <row r="10" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A10" s="13">
@@ -44766,9 +44779,9 @@
       <c r="O10" s="79">
         <v>0.56999999999999973</v>
       </c>
-      <c r="P10" s="158"/>
-      <c r="Q10" s="158"/>
-      <c r="R10" s="156"/>
+      <c r="P10" s="156"/>
+      <c r="Q10" s="156"/>
+      <c r="R10" s="154"/>
     </row>
     <row r="11" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A11" s="13">
@@ -44810,9 +44823,9 @@
       <c r="O11" s="79">
         <v>0.2280000000000002</v>
       </c>
-      <c r="P11" s="158"/>
-      <c r="Q11" s="158"/>
-      <c r="R11" s="156"/>
+      <c r="P11" s="156"/>
+      <c r="Q11" s="156"/>
+      <c r="R11" s="154"/>
     </row>
     <row r="12" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A12" s="13">
@@ -44854,13 +44867,13 @@
       <c r="O12" s="79">
         <v>2.3939999999999997</v>
       </c>
-      <c r="P12" s="158">
+      <c r="P12" s="156">
         <v>0.74754799177042697</v>
       </c>
-      <c r="Q12" s="158">
+      <c r="Q12" s="156">
         <v>2.7930000000000006</v>
       </c>
-      <c r="R12" s="156"/>
+      <c r="R12" s="154"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A13" s="13">
@@ -44902,9 +44915,9 @@
       <c r="O13" s="79">
         <v>3.42</v>
       </c>
-      <c r="P13" s="158"/>
-      <c r="Q13" s="158"/>
-      <c r="R13" s="156"/>
+      <c r="P13" s="156"/>
+      <c r="Q13" s="156"/>
+      <c r="R13" s="154"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A14" s="13">
@@ -44946,9 +44959,9 @@
       <c r="O14" s="79">
         <v>3.4200000000000008</v>
       </c>
-      <c r="P14" s="158"/>
-      <c r="Q14" s="158"/>
-      <c r="R14" s="156"/>
+      <c r="P14" s="156"/>
+      <c r="Q14" s="156"/>
+      <c r="R14" s="154"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A15" s="13">
@@ -44990,9 +45003,9 @@
       <c r="O15" s="79">
         <v>1.9380000000000002</v>
       </c>
-      <c r="P15" s="158"/>
-      <c r="Q15" s="158"/>
-      <c r="R15" s="157"/>
+      <c r="P15" s="156"/>
+      <c r="Q15" s="156"/>
+      <c r="R15" s="155"/>
     </row>
     <row r="16" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A16" s="13">
@@ -45034,13 +45047,13 @@
       <c r="O16" s="79">
         <v>0.91200000000000003</v>
       </c>
-      <c r="P16" s="158">
+      <c r="P16" s="156">
         <v>0.30161564946136354</v>
       </c>
-      <c r="Q16" s="158">
+      <c r="Q16" s="156">
         <v>0.5129999999999999</v>
       </c>
-      <c r="R16" s="155">
+      <c r="R16" s="153">
         <f>+ AVERAGE(O16:O27)</f>
         <v>0.5129999999999999</v>
       </c>
@@ -45085,9 +45098,9 @@
       <c r="O17" s="79">
         <v>0.22799999999999943</v>
       </c>
-      <c r="P17" s="158"/>
-      <c r="Q17" s="158"/>
-      <c r="R17" s="156"/>
+      <c r="P17" s="156"/>
+      <c r="Q17" s="156"/>
+      <c r="R17" s="154"/>
     </row>
     <row r="18" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A18" s="13">
@@ -45129,9 +45142,9 @@
       <c r="O18" s="79">
         <v>0.57000000000000051</v>
       </c>
-      <c r="P18" s="158"/>
-      <c r="Q18" s="158"/>
-      <c r="R18" s="156"/>
+      <c r="P18" s="156"/>
+      <c r="Q18" s="156"/>
+      <c r="R18" s="154"/>
     </row>
     <row r="19" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A19" s="13">
@@ -45173,9 +45186,9 @@
       <c r="O19" s="79">
         <v>0.34199999999999953</v>
       </c>
-      <c r="P19" s="158"/>
-      <c r="Q19" s="158"/>
-      <c r="R19" s="156"/>
+      <c r="P19" s="156"/>
+      <c r="Q19" s="156"/>
+      <c r="R19" s="154"/>
     </row>
     <row r="20" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A20" s="13">
@@ -45217,13 +45230,13 @@
       <c r="O20" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P20" s="158">
+      <c r="P20" s="156">
         <v>0.70505106198061995</v>
       </c>
-      <c r="Q20" s="158">
+      <c r="Q20" s="156">
         <v>0.54149999999999987</v>
       </c>
-      <c r="R20" s="156"/>
+      <c r="R20" s="154"/>
     </row>
     <row r="21" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A21" s="13">
@@ -45265,9 +45278,9 @@
       <c r="O21" s="79">
         <v>1.5959999999999999</v>
       </c>
-      <c r="P21" s="158"/>
-      <c r="Q21" s="158"/>
-      <c r="R21" s="156"/>
+      <c r="P21" s="156"/>
+      <c r="Q21" s="156"/>
+      <c r="R21" s="154"/>
     </row>
     <row r="22" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A22" s="13">
@@ -45309,9 +45322,9 @@
       <c r="O22" s="79">
         <v>0.2280000000000002</v>
       </c>
-      <c r="P22" s="158"/>
-      <c r="Q22" s="158"/>
-      <c r="R22" s="156"/>
+      <c r="P22" s="156"/>
+      <c r="Q22" s="156"/>
+      <c r="R22" s="154"/>
     </row>
     <row r="23" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A23" s="13">
@@ -45353,9 +45366,9 @@
       <c r="O23" s="79">
         <v>0.22799999999999943</v>
       </c>
-      <c r="P23" s="158"/>
-      <c r="Q23" s="158"/>
-      <c r="R23" s="156"/>
+      <c r="P23" s="156"/>
+      <c r="Q23" s="156"/>
+      <c r="R23" s="154"/>
     </row>
     <row r="24" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A24" s="13">
@@ -45397,13 +45410,13 @@
       <c r="O24" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P24" s="158">
+      <c r="P24" s="156">
         <v>0.34041298447620905</v>
       </c>
-      <c r="Q24" s="158">
+      <c r="Q24" s="156">
         <v>0.48450000000000004</v>
       </c>
-      <c r="R24" s="156"/>
+      <c r="R24" s="154"/>
     </row>
     <row r="25" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A25" s="13">
@@ -45445,9 +45458,9 @@
       <c r="O25" s="79">
         <v>0.91199999999999926</v>
       </c>
-      <c r="P25" s="158"/>
-      <c r="Q25" s="158"/>
-      <c r="R25" s="156"/>
+      <c r="P25" s="156"/>
+      <c r="Q25" s="156"/>
+      <c r="R25" s="154"/>
     </row>
     <row r="26" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A26" s="13">
@@ -45489,9 +45502,9 @@
       <c r="O26" s="79">
         <v>0.3420000000000003</v>
       </c>
-      <c r="P26" s="158"/>
-      <c r="Q26" s="158"/>
-      <c r="R26" s="156"/>
+      <c r="P26" s="156"/>
+      <c r="Q26" s="156"/>
+      <c r="R26" s="154"/>
     </row>
     <row r="27" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A27" s="13">
@@ -45533,9 +45546,9 @@
       <c r="O27" s="79">
         <v>0.57000000000000051</v>
       </c>
-      <c r="P27" s="158"/>
-      <c r="Q27" s="158"/>
-      <c r="R27" s="157"/>
+      <c r="P27" s="156"/>
+      <c r="Q27" s="156"/>
+      <c r="R27" s="155"/>
     </row>
     <row r="28" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A28" s="13">
@@ -45577,13 +45590,13 @@
       <c r="O28" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P28" s="158">
+      <c r="P28" s="156">
         <v>0.14717336715588197</v>
       </c>
-      <c r="Q28" s="158">
+      <c r="Q28" s="156">
         <v>0.17100000000000015</v>
       </c>
-      <c r="R28" s="155">
+      <c r="R28" s="153">
         <f>+AVERAGE(O28:O39)</f>
         <v>0.16150000000000014</v>
       </c>
@@ -45628,9 +45641,9 @@
       <c r="O29" s="79">
         <v>0</v>
       </c>
-      <c r="P29" s="158"/>
-      <c r="Q29" s="158"/>
-      <c r="R29" s="156"/>
+      <c r="P29" s="156"/>
+      <c r="Q29" s="156"/>
+      <c r="R29" s="154"/>
     </row>
     <row r="30" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A30" s="13">
@@ -45672,9 +45685,9 @@
       <c r="O30" s="79">
         <v>0.3420000000000003</v>
       </c>
-      <c r="P30" s="158"/>
-      <c r="Q30" s="158"/>
-      <c r="R30" s="156"/>
+      <c r="P30" s="156"/>
+      <c r="Q30" s="156"/>
+      <c r="R30" s="154"/>
     </row>
     <row r="31" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A31" s="13">
@@ -45716,9 +45729,9 @@
       <c r="O31" s="79">
         <v>0.2280000000000002</v>
       </c>
-      <c r="P31" s="158"/>
-      <c r="Q31" s="158"/>
-      <c r="R31" s="156"/>
+      <c r="P31" s="156"/>
+      <c r="Q31" s="156"/>
+      <c r="R31" s="154"/>
     </row>
     <row r="32" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A32" s="13">
@@ -45760,13 +45773,13 @@
       <c r="O32" s="79">
         <v>0</v>
       </c>
-      <c r="P32" s="158">
+      <c r="P32" s="156">
         <v>5.7000000000000058E-2</v>
       </c>
-      <c r="Q32" s="158">
+      <c r="Q32" s="156">
         <v>8.5500000000000076E-2</v>
       </c>
-      <c r="R32" s="156"/>
+      <c r="R32" s="154"/>
     </row>
     <row r="33" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A33" s="13">
@@ -45808,9 +45821,9 @@
       <c r="O33" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P33" s="158"/>
-      <c r="Q33" s="158"/>
-      <c r="R33" s="156"/>
+      <c r="P33" s="156"/>
+      <c r="Q33" s="156"/>
+      <c r="R33" s="154"/>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A34" s="13">
@@ -45852,9 +45865,9 @@
       <c r="O34" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P34" s="158"/>
-      <c r="Q34" s="158"/>
-      <c r="R34" s="156"/>
+      <c r="P34" s="156"/>
+      <c r="Q34" s="156"/>
+      <c r="R34" s="154"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A35" s="13">
@@ -45896,9 +45909,9 @@
       <c r="O35" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P35" s="158"/>
-      <c r="Q35" s="158"/>
-      <c r="R35" s="156"/>
+      <c r="P35" s="156"/>
+      <c r="Q35" s="156"/>
+      <c r="R35" s="154"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A36" s="13">
@@ -45940,13 +45953,13 @@
       <c r="O36" s="79">
         <v>0.3420000000000003</v>
       </c>
-      <c r="P36" s="158">
+      <c r="P36" s="156">
         <v>9.3080610225760835E-2</v>
       </c>
-      <c r="Q36" s="158">
+      <c r="Q36" s="156">
         <v>0.2280000000000002</v>
       </c>
-      <c r="R36" s="156"/>
+      <c r="R36" s="154"/>
     </row>
     <row r="37" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A37" s="13">
@@ -45988,9 +46001,9 @@
       <c r="O37" s="79">
         <v>0.2280000000000002</v>
       </c>
-      <c r="P37" s="158"/>
-      <c r="Q37" s="158"/>
-      <c r="R37" s="156"/>
+      <c r="P37" s="156"/>
+      <c r="Q37" s="156"/>
+      <c r="R37" s="154"/>
     </row>
     <row r="38" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A38" s="13">
@@ -46032,9 +46045,9 @@
       <c r="O38" s="79">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P38" s="158"/>
-      <c r="Q38" s="158"/>
-      <c r="R38" s="156"/>
+      <c r="P38" s="156"/>
+      <c r="Q38" s="156"/>
+      <c r="R38" s="154"/>
     </row>
     <row r="39" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A39" s="13">
@@ -46076,9 +46089,9 @@
       <c r="O39" s="79">
         <v>0.2280000000000002</v>
       </c>
-      <c r="P39" s="158"/>
-      <c r="Q39" s="158"/>
-      <c r="R39" s="157"/>
+      <c r="P39" s="156"/>
+      <c r="Q39" s="156"/>
+      <c r="R39" s="155"/>
     </row>
     <row r="40" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A40" s="13">
@@ -46120,13 +46133,13 @@
       <c r="O40" s="1">
         <v>0.56999999999999973</v>
       </c>
-      <c r="P40" s="155">
+      <c r="P40" s="153">
         <v>0.56234864630405212</v>
       </c>
-      <c r="Q40" s="155">
+      <c r="Q40" s="153">
         <v>0.83599999999999974</v>
       </c>
-      <c r="R40" s="155">
+      <c r="R40" s="153">
         <f>+AVERAGE(O40:O45)</f>
         <v>1.425</v>
       </c>
@@ -46171,9 +46184,9 @@
       <c r="O41" s="1">
         <v>0.45599999999999963</v>
       </c>
-      <c r="P41" s="156"/>
-      <c r="Q41" s="156"/>
-      <c r="R41" s="156"/>
+      <c r="P41" s="154"/>
+      <c r="Q41" s="154"/>
+      <c r="R41" s="154"/>
     </row>
     <row r="42" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A42" s="13">
@@ -46215,9 +46228,9 @@
       <c r="O42" s="1">
         <v>1.4819999999999998</v>
       </c>
-      <c r="P42" s="157"/>
-      <c r="Q42" s="157"/>
-      <c r="R42" s="156"/>
+      <c r="P42" s="155"/>
+      <c r="Q42" s="155"/>
+      <c r="R42" s="154"/>
     </row>
     <row r="43" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A43" s="13">
@@ -46259,13 +46272,13 @@
       <c r="O43" s="1">
         <v>3.0780000000000003</v>
       </c>
-      <c r="P43" s="155">
+      <c r="P43" s="153">
         <v>0.92847617093816626</v>
       </c>
-      <c r="Q43" s="155">
+      <c r="Q43" s="153">
         <v>2.0140000000000007</v>
       </c>
-      <c r="R43" s="156"/>
+      <c r="R43" s="154"/>
     </row>
     <row r="44" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A44" s="13">
@@ -46307,9 +46320,9 @@
       <c r="O44" s="1">
         <v>1.3680000000000005</v>
       </c>
-      <c r="P44" s="156"/>
-      <c r="Q44" s="156"/>
-      <c r="R44" s="156"/>
+      <c r="P44" s="154"/>
+      <c r="Q44" s="154"/>
+      <c r="R44" s="154"/>
     </row>
     <row r="45" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A45" s="13">
@@ -46351,9 +46364,9 @@
       <c r="O45" s="1">
         <v>1.5960000000000008</v>
       </c>
-      <c r="P45" s="157"/>
-      <c r="Q45" s="157"/>
-      <c r="R45" s="156"/>
+      <c r="P45" s="155"/>
+      <c r="Q45" s="155"/>
+      <c r="R45" s="154"/>
     </row>
     <row r="46" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A46" s="13">
@@ -46392,12 +46405,12 @@
       <c r="N46" s="1" t="s">
         <v>494</v>
       </c>
-      <c r="O46" s="159" t="s">
+      <c r="O46" s="157" t="s">
         <v>501</v>
       </c>
-      <c r="P46" s="160"/>
-      <c r="Q46" s="161"/>
-      <c r="R46" s="156"/>
+      <c r="P46" s="158"/>
+      <c r="Q46" s="159"/>
+      <c r="R46" s="154"/>
     </row>
     <row r="47" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A47" s="13">
@@ -46436,10 +46449,10 @@
       <c r="N47" s="1" t="s">
         <v>495</v>
       </c>
-      <c r="O47" s="162"/>
-      <c r="P47" s="163"/>
-      <c r="Q47" s="164"/>
-      <c r="R47" s="156"/>
+      <c r="O47" s="160"/>
+      <c r="P47" s="161"/>
+      <c r="Q47" s="162"/>
+      <c r="R47" s="154"/>
     </row>
     <row r="48" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A48" s="13">
@@ -46478,10 +46491,10 @@
       <c r="N48" s="1" t="s">
         <v>496</v>
       </c>
-      <c r="O48" s="165"/>
-      <c r="P48" s="166"/>
-      <c r="Q48" s="167"/>
-      <c r="R48" s="157"/>
+      <c r="O48" s="163"/>
+      <c r="P48" s="164"/>
+      <c r="Q48" s="165"/>
+      <c r="R48" s="155"/>
     </row>
     <row r="49" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A49" s="13">
@@ -46523,13 +46536,13 @@
       <c r="O49" s="1">
         <v>1.1399999999999995</v>
       </c>
-      <c r="P49" s="155">
+      <c r="P49" s="153">
         <v>1.4554545681676232</v>
       </c>
-      <c r="Q49" s="155">
+      <c r="Q49" s="153">
         <v>2.3939999999999997</v>
       </c>
-      <c r="R49" s="155">
+      <c r="R49" s="153">
         <f>+AVERAGE(O49:O57)</f>
         <v>5.9660000000000002</v>
       </c>
@@ -46574,9 +46587,9 @@
       <c r="O50" s="1">
         <v>3.9900000000000007</v>
       </c>
-      <c r="P50" s="156"/>
-      <c r="Q50" s="156"/>
-      <c r="R50" s="156"/>
+      <c r="P50" s="154"/>
+      <c r="Q50" s="154"/>
+      <c r="R50" s="154"/>
     </row>
     <row r="51" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A51" s="13">
@@ -46618,9 +46631,9 @@
       <c r="O51" s="1">
         <v>2.0519999999999996</v>
       </c>
-      <c r="P51" s="157"/>
-      <c r="Q51" s="157"/>
-      <c r="R51" s="156"/>
+      <c r="P51" s="155"/>
+      <c r="Q51" s="155"/>
+      <c r="R51" s="154"/>
     </row>
     <row r="52" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A52" s="13">
@@ -46662,13 +46675,13 @@
       <c r="O52" s="1">
         <v>0.45599999999999963</v>
       </c>
-      <c r="P52" s="155">
+      <c r="P52" s="153">
         <v>0.23730992393913886</v>
       </c>
-      <c r="Q52" s="155">
+      <c r="Q52" s="153">
         <v>0.37999999999999984</v>
       </c>
-      <c r="R52" s="156"/>
+      <c r="R52" s="154"/>
     </row>
     <row r="53" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A53" s="13">
@@ -46710,9 +46723,9 @@
       <c r="O53" s="1">
         <v>0.56999999999999973</v>
       </c>
-      <c r="P53" s="156"/>
-      <c r="Q53" s="156"/>
-      <c r="R53" s="156"/>
+      <c r="P53" s="154"/>
+      <c r="Q53" s="154"/>
+      <c r="R53" s="154"/>
     </row>
     <row r="54" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A54" s="13">
@@ -46754,9 +46767,9 @@
       <c r="O54" s="1">
         <v>0.1140000000000001</v>
       </c>
-      <c r="P54" s="157"/>
-      <c r="Q54" s="157"/>
-      <c r="R54" s="156"/>
+      <c r="P54" s="155"/>
+      <c r="Q54" s="155"/>
+      <c r="R54" s="154"/>
     </row>
     <row r="55" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A55" s="13">
@@ -46798,13 +46811,13 @@
       <c r="O55" s="1">
         <v>7.5240000000000009</v>
       </c>
-      <c r="P55" s="155">
+      <c r="P55" s="153">
         <v>7.1723427135072155</v>
       </c>
-      <c r="Q55" s="155">
+      <c r="Q55" s="153">
         <v>15.124000000000001</v>
       </c>
-      <c r="R55" s="156"/>
+      <c r="R55" s="154"/>
     </row>
     <row r="56" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A56" s="13">
@@ -46846,9 +46859,9 @@
       <c r="O56" s="1">
         <v>16.073999999999998</v>
       </c>
-      <c r="P56" s="156"/>
-      <c r="Q56" s="156"/>
-      <c r="R56" s="156"/>
+      <c r="P56" s="154"/>
+      <c r="Q56" s="154"/>
+      <c r="R56" s="154"/>
     </row>
     <row r="57" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A57" s="13">
@@ -46890,9 +46903,9 @@
       <c r="O57" s="1">
         <v>21.774000000000001</v>
       </c>
-      <c r="P57" s="157"/>
-      <c r="Q57" s="157"/>
-      <c r="R57" s="157"/>
+      <c r="P57" s="155"/>
+      <c r="Q57" s="155"/>
+      <c r="R57" s="155"/>
     </row>
     <row r="58" spans="1:18" x14ac:dyDescent="0.25">
       <c r="A58" s="13">
@@ -51855,24 +51868,6 @@
     </row>
   </sheetData>
   <mergeCells count="34">
-    <mergeCell ref="P43:P45"/>
-    <mergeCell ref="Q43:Q45"/>
-    <mergeCell ref="R40:R48"/>
-    <mergeCell ref="P28:P31"/>
-    <mergeCell ref="Q28:Q31"/>
-    <mergeCell ref="P32:P35"/>
-    <mergeCell ref="Q32:Q35"/>
-    <mergeCell ref="P40:P42"/>
-    <mergeCell ref="Q40:Q42"/>
-    <mergeCell ref="Q36:Q39"/>
-    <mergeCell ref="R49:R57"/>
-    <mergeCell ref="O46:Q48"/>
-    <mergeCell ref="P49:P51"/>
-    <mergeCell ref="Q49:Q51"/>
-    <mergeCell ref="P52:P54"/>
-    <mergeCell ref="Q52:Q54"/>
-    <mergeCell ref="P55:P57"/>
-    <mergeCell ref="Q55:Q57"/>
     <mergeCell ref="R4:R15"/>
     <mergeCell ref="R16:R27"/>
     <mergeCell ref="R28:R39"/>
@@ -51889,6 +51884,24 @@
     <mergeCell ref="P24:P27"/>
     <mergeCell ref="Q24:Q27"/>
     <mergeCell ref="P36:P39"/>
+    <mergeCell ref="R49:R57"/>
+    <mergeCell ref="O46:Q48"/>
+    <mergeCell ref="P49:P51"/>
+    <mergeCell ref="Q49:Q51"/>
+    <mergeCell ref="P52:P54"/>
+    <mergeCell ref="Q52:Q54"/>
+    <mergeCell ref="P55:P57"/>
+    <mergeCell ref="Q55:Q57"/>
+    <mergeCell ref="P43:P45"/>
+    <mergeCell ref="Q43:Q45"/>
+    <mergeCell ref="R40:R48"/>
+    <mergeCell ref="P28:P31"/>
+    <mergeCell ref="Q28:Q31"/>
+    <mergeCell ref="P32:P35"/>
+    <mergeCell ref="Q32:Q35"/>
+    <mergeCell ref="P40:P42"/>
+    <mergeCell ref="Q40:Q42"/>
+    <mergeCell ref="Q36:Q39"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
@@ -51925,18 +51938,18 @@
       <c r="A5" s="144" t="s">
         <v>455</v>
       </c>
-      <c r="B5" s="148" t="s">
+      <c r="B5" s="141" t="s">
         <v>809</v>
       </c>
-      <c r="C5" s="150" t="s">
+      <c r="C5" s="140" t="s">
         <v>480</v>
       </c>
-      <c r="D5" s="150"/>
-      <c r="E5" s="150"/>
+      <c r="D5" s="140"/>
+      <c r="E5" s="140"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="144"/>
-      <c r="B6" s="149"/>
+      <c r="B6" s="142"/>
       <c r="C6" s="5" t="s">
         <v>33</v>
       </c>
@@ -52251,22 +52264,22 @@
       <c r="A26" s="144" t="s">
         <v>455</v>
       </c>
-      <c r="B26" s="148" t="s">
+      <c r="B26" s="141" t="s">
         <v>809</v>
       </c>
-      <c r="C26" s="171" t="s">
+      <c r="C26" s="170" t="s">
         <v>826</v>
       </c>
-      <c r="D26" s="172" t="s">
+      <c r="D26" s="171" t="s">
         <v>235</v>
       </c>
-      <c r="E26" s="172"/>
-      <c r="F26" s="172"/>
+      <c r="E26" s="171"/>
+      <c r="F26" s="171"/>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="144"/>
-      <c r="B27" s="149"/>
-      <c r="C27" s="171"/>
+      <c r="B27" s="142"/>
+      <c r="C27" s="170"/>
       <c r="D27" s="112"/>
       <c r="E27" s="112"/>
     </row>
@@ -52487,18 +52500,18 @@
       <c r="A46" s="144" t="s">
         <v>455</v>
       </c>
-      <c r="B46" s="148" t="s">
+      <c r="B46" s="141" t="s">
         <v>809</v>
       </c>
-      <c r="C46" s="168" t="s">
+      <c r="C46" s="167" t="s">
         <v>834</v>
       </c>
-      <c r="D46" s="169"/>
-      <c r="E46" s="170"/>
+      <c r="D46" s="168"/>
+      <c r="E46" s="169"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="144"/>
-      <c r="B47" s="149"/>
+      <c r="B47" s="142"/>
       <c r="C47" s="5" t="s">
         <v>33</v>
       </c>
@@ -52685,27 +52698,27 @@
       </c>
     </row>
     <row r="67" spans="1:9" ht="48" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="119" t="s">
+      <c r="A67" s="166" t="s">
         <v>835</v>
       </c>
-      <c r="B67" s="119"/>
-      <c r="C67" s="119"/>
-      <c r="D67" s="119"/>
-      <c r="E67" s="119"/>
-      <c r="F67" s="119"/>
-      <c r="G67" s="119"/>
-      <c r="H67" s="119"/>
-      <c r="I67" s="119"/>
+      <c r="B67" s="166"/>
+      <c r="C67" s="166"/>
+      <c r="D67" s="166"/>
+      <c r="E67" s="166"/>
+      <c r="F67" s="166"/>
+      <c r="G67" s="166"/>
+      <c r="H67" s="166"/>
+      <c r="I67" s="166"/>
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" s="144" t="s">
         <v>129</v>
       </c>
-      <c r="B69" s="150" t="s">
+      <c r="B69" s="140" t="s">
         <v>480</v>
       </c>
-      <c r="C69" s="150"/>
-      <c r="D69" s="150"/>
+      <c r="C69" s="140"/>
+      <c r="D69" s="140"/>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" s="144"/>
